--- a/1.training_model/supplementary/Data Tabulation - Flowchart.xlsx
+++ b/1.training_model/supplementary/Data Tabulation - Flowchart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sitisyaziyah\source\repos\DeviceCluster\1.training_model\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD0E266-0574-4133-946C-BC5074C83765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A10780F-3F7D-46DD-A140-9ABCD75F2469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="717" activeTab="5" xr2:uid="{E471D6E3-533D-4285-ABDC-6FF3DFDEE99D}"/>
   </bookViews>
@@ -17,17 +17,17 @@
     <sheet name="Stage 1" sheetId="4" r:id="rId2"/>
     <sheet name="Stage 2" sheetId="6" r:id="rId3"/>
     <sheet name="Stage 3" sheetId="7" r:id="rId4"/>
-    <sheet name="Stage 4" sheetId="8" r:id="rId5"/>
-    <sheet name="Stage 4 (2)" sheetId="13" r:id="rId6"/>
+    <sheet name="Stage 4" sheetId="13" r:id="rId5"/>
+    <sheet name="draft" sheetId="15" r:id="rId6"/>
     <sheet name="Example case" sheetId="12" r:id="rId7"/>
     <sheet name="transpose" sheetId="3" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Stage 1'!$B$2:$H$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">draft!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Stage 1'!$B$1:$H$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Stage 2'!$B$2:$H$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stage 3'!$B$2:$H$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Stage 4'!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Stage 4 (2)'!#REF!</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">transpose!$B$3:$AE$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="67">
   <si>
     <t>Device ID</t>
   </si>
@@ -241,12 +241,24 @@
   <si>
     <t>Catagorize Device ID by each  cluster group</t>
   </si>
+  <si>
+    <t>Sort the highest percentage for each cluster</t>
+  </si>
+  <si>
+    <t>VACANT</t>
+  </si>
+  <si>
+    <t>Control Valve</t>
+  </si>
+  <si>
+    <t>Check the vacant and extra</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,8 +282,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -311,6 +331,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -355,10 +381,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -399,8 +426,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -421,15 +464,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>499242</xdr:colOff>
+      <xdr:colOff>485589</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>123519</xdr:rowOff>
+      <xdr:rowOff>140157</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>160338</xdr:colOff>
+      <xdr:colOff>146685</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>101929</xdr:rowOff>
+      <xdr:rowOff>118567</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -444,8 +487,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6746328" y="1411036"/>
-          <a:ext cx="2104751" cy="543341"/>
+          <a:off x="6722276" y="1412401"/>
+          <a:ext cx="2097881" cy="543852"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -498,15 +541,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>160338</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>168808</xdr:rowOff>
+      <xdr:colOff>143510</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>33060</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>371346</xdr:colOff>
+      <xdr:colOff>354708</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>20759</xdr:rowOff>
+      <xdr:rowOff>41663</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -524,8 +567,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="8851079" y="1640256"/>
-          <a:ext cx="2654664" cy="42451"/>
+          <a:off x="8816982" y="1678899"/>
+          <a:ext cx="2647982" cy="8603"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -554,15 +597,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>374521</xdr:colOff>
+      <xdr:colOff>357883</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>48816</xdr:rowOff>
+      <xdr:rowOff>99301</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>579674</xdr:colOff>
+      <xdr:colOff>569386</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>94906</xdr:rowOff>
+      <xdr:rowOff>142216</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -577,8 +620,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11490196" y="1315641"/>
-          <a:ext cx="2033953" cy="608065"/>
+          <a:off x="11468139" y="1371545"/>
+          <a:ext cx="2039092" cy="608357"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -635,15 +678,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>329790</xdr:colOff>
+      <xdr:colOff>316137</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>45641</xdr:rowOff>
+      <xdr:rowOff>102476</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>171641</xdr:colOff>
+      <xdr:colOff>157450</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>123519</xdr:rowOff>
+      <xdr:rowOff>143332</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -661,12 +704,12 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000" flipH="1" flipV="1">
-          <a:off x="10124346" y="-992484"/>
-          <a:ext cx="77878" cy="4729161"/>
+          <a:off x="10108230" y="-962293"/>
+          <a:ext cx="40856" cy="4714881"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -293536"/>
+            <a:gd name="adj1" fmla="val -559526"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -829,15 +872,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>245012</xdr:colOff>
+      <xdr:colOff>216640</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>168820</xdr:rowOff>
+      <xdr:rowOff>164766</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>406937</xdr:colOff>
+      <xdr:colOff>381740</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>112995</xdr:rowOff>
+      <xdr:rowOff>108941</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -852,8 +895,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6492098" y="2573061"/>
-          <a:ext cx="2605580" cy="312037"/>
+          <a:off x="6450449" y="2552096"/>
+          <a:ext cx="2597014" cy="308962"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -906,15 +949,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>327562</xdr:colOff>
+      <xdr:colOff>300778</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>105104</xdr:rowOff>
+      <xdr:rowOff>121742</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>332965</xdr:colOff>
+      <xdr:colOff>316137</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>168820</xdr:rowOff>
+      <xdr:rowOff>161591</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -932,8 +975,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="7796476" y="1957552"/>
-          <a:ext cx="5403" cy="615509"/>
+          <a:off x="7750544" y="1961891"/>
+          <a:ext cx="15359" cy="587030"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1020,9 +1063,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>576384</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>107462</xdr:rowOff>
+      <xdr:colOff>587666</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>156978</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="346826" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -1038,7 +1081,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6530730" y="1973385"/>
+          <a:off x="7429453" y="2179521"/>
           <a:ext cx="346826" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1078,15 +1121,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>245672</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>24221</xdr:rowOff>
+      <xdr:colOff>213246</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>153045</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>416981</xdr:colOff>
+      <xdr:colOff>384555</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>107046</xdr:rowOff>
+      <xdr:rowOff>47126</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1101,8 +1144,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6492758" y="3348118"/>
-          <a:ext cx="2614964" cy="450687"/>
+          <a:off x="6447055" y="3269949"/>
+          <a:ext cx="2603223" cy="441262"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1155,15 +1198,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>327562</xdr:colOff>
+      <xdr:colOff>300778</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>112995</xdr:rowOff>
+      <xdr:rowOff>105766</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>331326</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>27396</xdr:rowOff>
+      <xdr:colOff>302076</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>153045</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1181,8 +1224,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7796476" y="2885098"/>
-          <a:ext cx="3764" cy="466195"/>
+          <a:off x="7750544" y="2857883"/>
+          <a:ext cx="1298" cy="412066"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1211,15 +1254,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>160338</xdr:colOff>
+      <xdr:colOff>146685</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>20759</xdr:rowOff>
+      <xdr:rowOff>34222</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>207031</xdr:colOff>
+      <xdr:colOff>190203</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>114848</xdr:rowOff>
+      <xdr:rowOff>128311</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1236,8 +1279,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8851079" y="1682707"/>
-          <a:ext cx="2490349" cy="1388175"/>
+          <a:off x="8820157" y="1680061"/>
+          <a:ext cx="2480302" cy="1376430"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1780,7 +1823,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EFAC392-3DBC-4888-8676-CE4E321B2BF1}">
-  <dimension ref="B2:Q31"/>
+  <dimension ref="B1:Q30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -1794,74 +1837,112 @@
     <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O1" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B2" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="10" t="s">
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2">
+        <v>68.8</v>
+      </c>
+      <c r="E2">
+        <v>83.4</v>
+      </c>
+      <c r="F2">
+        <v>19.8</v>
+      </c>
+      <c r="G2">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="H2" s="4">
+        <v>84</v>
+      </c>
+      <c r="K2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="10" t="s">
+      <c r="N2">
         <v>3</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="10" t="s">
+      <c r="O2" s="12">
         <v>6</v>
-      </c>
-      <c r="L2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N2" t="s">
-        <v>40</v>
-      </c>
-      <c r="O2" s="12" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
       <c r="D3">
-        <v>68.8</v>
+        <v>69.2</v>
       </c>
       <c r="E3">
-        <v>83.4</v>
-      </c>
-      <c r="F3">
-        <v>19.8</v>
+        <v>83</v>
+      </c>
+      <c r="F3" s="4">
+        <v>91</v>
       </c>
       <c r="G3">
-        <v>38.200000000000003</v>
-      </c>
-      <c r="H3" s="4">
-        <v>84</v>
+        <v>56.2</v>
+      </c>
+      <c r="H3">
+        <v>79.8</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O3" s="12">
         <v>6</v>
@@ -1869,760 +1950,722 @@
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4">
-        <v>69.2</v>
+        <v>19.8</v>
       </c>
       <c r="E4">
-        <v>83</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="F4" s="4">
-        <v>91</v>
+        <v>95.3</v>
       </c>
       <c r="G4">
-        <v>56.2</v>
+        <v>12.4</v>
       </c>
       <c r="H4">
-        <v>79.8</v>
+        <v>57.9</v>
       </c>
       <c r="K4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4" s="12">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D5">
-        <v>19.8</v>
+      <c r="D5" s="4">
+        <v>98.5</v>
       </c>
       <c r="E5">
-        <v>33.200000000000003</v>
-      </c>
-      <c r="F5" s="4">
-        <v>95.3</v>
+        <v>84.4</v>
+      </c>
+      <c r="F5">
+        <v>7.2</v>
       </c>
       <c r="G5">
-        <v>12.4</v>
+        <v>83</v>
       </c>
       <c r="H5">
-        <v>57.9</v>
+        <v>31.2</v>
       </c>
       <c r="K5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M5">
         <v>1</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O5" s="12">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="4">
-        <v>98.5</v>
+      <c r="D6">
+        <v>39.6</v>
       </c>
       <c r="E6">
-        <v>84.4</v>
+        <v>1.3</v>
       </c>
       <c r="F6">
-        <v>7.2</v>
+        <v>54.9</v>
       </c>
       <c r="G6">
-        <v>83</v>
-      </c>
-      <c r="H6">
-        <v>31.2</v>
+        <v>26.3</v>
+      </c>
+      <c r="H6" s="4">
+        <v>65</v>
       </c>
       <c r="K6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O6" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
       <c r="D7">
-        <v>39.6</v>
-      </c>
-      <c r="E7">
-        <v>1.3</v>
+        <v>67.900000000000006</v>
+      </c>
+      <c r="E7" s="4">
+        <v>84.7</v>
       </c>
       <c r="F7">
-        <v>54.9</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="G7">
-        <v>26.3</v>
-      </c>
-      <c r="H7" s="4">
-        <v>65</v>
-      </c>
-      <c r="K7" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
+        <v>21.3</v>
+      </c>
+      <c r="H7">
+        <v>43.2</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L7" s="11">
+        <v>10</v>
+      </c>
+      <c r="M7" s="11">
         <v>5</v>
       </c>
-      <c r="O7" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="N7" s="11">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8">
-        <v>67.900000000000006</v>
-      </c>
-      <c r="E8" s="4">
-        <v>84.7</v>
+        <v>44.5</v>
+      </c>
+      <c r="E8">
+        <v>16.8</v>
       </c>
       <c r="F8">
-        <v>35.700000000000003</v>
-      </c>
-      <c r="G8">
-        <v>21.3</v>
+        <v>73.099999999999994</v>
+      </c>
+      <c r="G8" s="4">
+        <v>76.400000000000006</v>
       </c>
       <c r="H8">
-        <v>43.2</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="L8" s="11">
-        <v>10</v>
-      </c>
-      <c r="M8" s="11">
-        <v>5</v>
-      </c>
-      <c r="N8" s="11">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="2:17" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="D9">
-        <v>44.5</v>
+        <v>46.3</v>
       </c>
       <c r="E9">
-        <v>16.8</v>
-      </c>
-      <c r="F9">
-        <v>73.099999999999994</v>
-      </c>
-      <c r="G9" s="4">
-        <v>76.400000000000006</v>
+        <v>24.1</v>
+      </c>
+      <c r="F9" s="4">
+        <v>87.1</v>
+      </c>
+      <c r="G9">
+        <v>47.8</v>
       </c>
       <c r="H9">
-        <v>8.6</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
       </c>
-      <c r="D10">
-        <v>46.3</v>
+      <c r="D10" s="4">
+        <v>96.8</v>
       </c>
       <c r="E10">
-        <v>24.1</v>
-      </c>
-      <c r="F10" s="4">
-        <v>87.1</v>
+        <v>64.900000000000006</v>
+      </c>
+      <c r="F10">
+        <v>7</v>
       </c>
       <c r="G10">
-        <v>47.8</v>
+        <v>78.8</v>
       </c>
       <c r="H10">
-        <v>30.2</v>
-      </c>
-    </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="4">
-        <v>96.8</v>
-      </c>
-      <c r="E11">
-        <v>64.900000000000006</v>
-      </c>
-      <c r="F11">
-        <v>7</v>
-      </c>
-      <c r="G11">
-        <v>78.8</v>
-      </c>
-      <c r="H11">
         <v>22.2</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K10" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="13" t="s">
+      <c r="L10" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-    </row>
-    <row r="12" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+    </row>
+    <row r="11" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="9">
+      <c r="C11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="9">
         <v>78.900000000000006</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E11" s="9">
         <v>84</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F11" s="9">
         <v>22.4</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G11" s="17">
         <v>89.1</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H11" s="9">
         <v>35.700000000000003</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K11" t="s">
         <v>50</v>
       </c>
+      <c r="L11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12">
+        <v>50.9</v>
+      </c>
+      <c r="E12">
+        <v>46</v>
+      </c>
+      <c r="F12">
+        <v>7.2</v>
+      </c>
+      <c r="G12">
+        <v>7.4</v>
+      </c>
+      <c r="H12" s="4">
+        <v>90.3</v>
+      </c>
       <c r="L12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
       </c>
-      <c r="D13">
-        <v>50.9</v>
+      <c r="D13" s="4">
+        <v>76.7</v>
       </c>
       <c r="E13">
-        <v>46</v>
+        <v>52.8</v>
       </c>
       <c r="F13">
-        <v>7.2</v>
+        <v>1.3</v>
       </c>
       <c r="G13">
-        <v>7.4</v>
-      </c>
-      <c r="H13" s="4">
-        <v>90.3</v>
-      </c>
-      <c r="L13" t="s">
-        <v>52</v>
+        <v>0.7</v>
+      </c>
+      <c r="H13">
+        <v>19.7</v>
+      </c>
+      <c r="L13" s="18" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="4">
-        <v>76.7</v>
+      <c r="D14">
+        <v>28.3</v>
       </c>
       <c r="E14">
-        <v>52.8</v>
+        <v>40.4</v>
       </c>
       <c r="F14">
-        <v>1.3</v>
+        <v>12.6</v>
       </c>
       <c r="G14">
-        <v>0.7</v>
-      </c>
-      <c r="H14">
-        <v>19.7</v>
-      </c>
-      <c r="L14" s="18" t="s">
-        <v>55</v>
+        <v>43.9</v>
+      </c>
+      <c r="H14" s="4">
+        <v>84.7</v>
+      </c>
+      <c r="L14" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
         <v>19</v>
       </c>
       <c r="D15">
-        <v>28.3</v>
+        <v>8.5</v>
       </c>
       <c r="E15">
-        <v>40.4</v>
+        <v>60.3</v>
       </c>
       <c r="F15">
-        <v>12.6</v>
+        <v>27.9</v>
       </c>
       <c r="G15">
-        <v>43.9</v>
+        <v>31.8</v>
       </c>
       <c r="H15" s="4">
-        <v>84.7</v>
+        <v>66.7</v>
+      </c>
+      <c r="K15" t="s">
+        <v>54</v>
       </c>
       <c r="L15" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" t="s">
+    <row r="16" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D16">
-        <v>8.5</v>
-      </c>
-      <c r="E16">
-        <v>60.3</v>
-      </c>
-      <c r="F16">
-        <v>27.9</v>
-      </c>
-      <c r="G16">
-        <v>31.8</v>
-      </c>
-      <c r="H16" s="4">
-        <v>66.7</v>
+      <c r="D16" s="9">
+        <v>14.3</v>
+      </c>
+      <c r="E16" s="9">
+        <v>45</v>
+      </c>
+      <c r="F16" s="17">
+        <v>73.3</v>
+      </c>
+      <c r="G16" s="9">
+        <v>51.8</v>
+      </c>
+      <c r="H16" s="9">
+        <v>36.1</v>
       </c>
       <c r="K16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="9">
-        <v>14.3</v>
-      </c>
-      <c r="E17" s="9">
-        <v>45</v>
-      </c>
-      <c r="F17" s="17">
-        <v>73.3</v>
-      </c>
-      <c r="G17" s="9">
-        <v>51.8</v>
-      </c>
-      <c r="H17" s="9">
-        <v>36.1</v>
-      </c>
-      <c r="K17" t="s">
-        <v>56</v>
-      </c>
-      <c r="L17" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17">
+        <v>47.4</v>
+      </c>
+      <c r="E17">
+        <v>72.5</v>
+      </c>
+      <c r="F17">
+        <v>74.900000000000006</v>
+      </c>
+      <c r="G17" s="4">
+        <v>84.3</v>
+      </c>
+      <c r="H17">
+        <v>18.899999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
         <v>25</v>
       </c>
       <c r="D18">
-        <v>47.4</v>
-      </c>
-      <c r="E18">
-        <v>72.5</v>
+        <v>58.9</v>
+      </c>
+      <c r="E18" s="4">
+        <v>99</v>
       </c>
       <c r="F18">
-        <v>74.900000000000006</v>
-      </c>
-      <c r="G18" s="4">
-        <v>84.3</v>
+        <v>92.4</v>
+      </c>
+      <c r="G18">
+        <v>57.6</v>
       </c>
       <c r="H18">
-        <v>18.899999999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
+        <v>89.7</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
         <v>25</v>
       </c>
       <c r="D19">
-        <v>58.9</v>
-      </c>
-      <c r="E19" s="4">
-        <v>99</v>
-      </c>
-      <c r="F19">
-        <v>92.4</v>
+        <v>55.1</v>
+      </c>
+      <c r="E19">
+        <v>20.9</v>
+      </c>
+      <c r="F19" s="4">
+        <v>86</v>
       </c>
       <c r="G19">
-        <v>57.6</v>
+        <v>77.8</v>
       </c>
       <c r="H19">
-        <v>89.7</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
       </c>
       <c r="D20">
-        <v>55.1</v>
+        <v>16.3</v>
       </c>
       <c r="E20">
-        <v>20.9</v>
-      </c>
-      <c r="F20" s="4">
-        <v>86</v>
-      </c>
-      <c r="G20">
-        <v>77.8</v>
+        <v>22.8</v>
+      </c>
+      <c r="F20">
+        <v>82</v>
+      </c>
+      <c r="G20" s="4">
+        <v>96.9</v>
       </c>
       <c r="H20">
-        <v>54.7</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
         <v>25</v>
       </c>
-      <c r="D21">
-        <v>16.3</v>
+      <c r="D21" s="4">
+        <v>83.9</v>
       </c>
       <c r="E21">
-        <v>22.8</v>
+        <v>4.8</v>
       </c>
       <c r="F21">
-        <v>82</v>
-      </c>
-      <c r="G21" s="4">
-        <v>96.9</v>
+        <v>70.2</v>
+      </c>
+      <c r="G21">
+        <v>58.1</v>
       </c>
       <c r="H21">
-        <v>28.7</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="4">
-        <v>83.9</v>
+        <v>70</v>
       </c>
       <c r="E22">
+        <v>5.9</v>
+      </c>
+      <c r="F22">
+        <v>26.7</v>
+      </c>
+      <c r="G22">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="H22">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23">
+        <v>52.5</v>
+      </c>
+      <c r="E23">
+        <v>71.5</v>
+      </c>
+      <c r="F23">
+        <v>7</v>
+      </c>
+      <c r="G23">
+        <v>70.3</v>
+      </c>
+      <c r="H23" s="4">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24">
+        <v>3.4</v>
+      </c>
+      <c r="E24">
+        <v>63.3</v>
+      </c>
+      <c r="F24">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="G24" s="4">
+        <v>70.5</v>
+      </c>
+      <c r="H24">
+        <v>63.8</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25">
+        <v>57.9</v>
+      </c>
+      <c r="E25">
+        <v>50.4</v>
+      </c>
+      <c r="F25">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G25" s="4">
+        <v>63.4</v>
+      </c>
+      <c r="H25">
         <v>4.8</v>
       </c>
-      <c r="F22">
-        <v>70.2</v>
-      </c>
-      <c r="G22">
-        <v>58.1</v>
-      </c>
-      <c r="H22">
-        <v>46.3</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B23" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="4">
-        <v>70</v>
-      </c>
-      <c r="E23">
-        <v>5.9</v>
-      </c>
-      <c r="F23">
-        <v>26.7</v>
-      </c>
-      <c r="G23">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="H23">
-        <v>41.7</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24">
-        <v>52.5</v>
-      </c>
-      <c r="E24">
-        <v>71.5</v>
-      </c>
-      <c r="F24">
-        <v>7</v>
-      </c>
-      <c r="G24">
-        <v>70.3</v>
-      </c>
-      <c r="H24" s="4">
-        <v>91.7</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25">
-        <v>3.4</v>
-      </c>
-      <c r="E25">
-        <v>63.3</v>
-      </c>
-      <c r="F25">
-        <v>36.200000000000003</v>
-      </c>
-      <c r="G25" s="4">
-        <v>70.5</v>
-      </c>
-      <c r="H25">
-        <v>63.8</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
         <v>25</v>
       </c>
       <c r="D26">
-        <v>57.9</v>
-      </c>
-      <c r="E26">
-        <v>50.4</v>
+        <v>93.4</v>
+      </c>
+      <c r="E26" s="4">
+        <v>95.8</v>
       </c>
       <c r="F26">
+        <v>58.4</v>
+      </c>
+      <c r="G26">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="H26">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="E27" s="4">
+        <v>93.3</v>
+      </c>
+      <c r="F27">
+        <v>64.900000000000006</v>
+      </c>
+      <c r="G27">
+        <v>63.2</v>
+      </c>
+      <c r="H27">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28">
+        <v>15.6</v>
+      </c>
+      <c r="E28" s="4">
+        <v>77.599999999999994</v>
+      </c>
+      <c r="F28">
+        <v>24.3</v>
+      </c>
+      <c r="G28">
+        <v>5.3</v>
+      </c>
+      <c r="H28">
+        <v>53.5</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29">
+        <v>17.2</v>
+      </c>
+      <c r="E29">
+        <v>13.3</v>
+      </c>
+      <c r="F29" s="4">
+        <v>48.1</v>
+      </c>
+      <c r="G29">
+        <v>31.2</v>
+      </c>
+      <c r="H29">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G26" s="4">
-        <v>63.4</v>
-      </c>
-      <c r="H26">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B27" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" t="s">
-        <v>25</v>
-      </c>
-      <c r="D27">
-        <v>93.4</v>
-      </c>
-      <c r="E27" s="4">
-        <v>95.8</v>
-      </c>
-      <c r="F27">
-        <v>58.4</v>
-      </c>
-      <c r="G27">
-        <v>81.599999999999994</v>
-      </c>
-      <c r="H27">
-        <v>29.2</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B28" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="E28" s="4">
-        <v>93.3</v>
-      </c>
-      <c r="F28">
-        <v>64.900000000000006</v>
-      </c>
-      <c r="G28">
-        <v>63.2</v>
-      </c>
-      <c r="H28">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B29" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29">
-        <v>15.6</v>
-      </c>
-      <c r="E29" s="4">
-        <v>77.599999999999994</v>
-      </c>
-      <c r="F29">
-        <v>24.3</v>
-      </c>
-      <c r="G29">
-        <v>5.3</v>
-      </c>
-      <c r="H29">
-        <v>53.5</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" t="s">
-        <v>25</v>
-      </c>
-      <c r="D30">
-        <v>17.2</v>
-      </c>
       <c r="E30">
-        <v>13.3</v>
-      </c>
-      <c r="F30" s="4">
-        <v>48.1</v>
-      </c>
-      <c r="G30">
-        <v>31.2</v>
+        <v>9.9</v>
+      </c>
+      <c r="F30">
+        <v>60.4</v>
+      </c>
+      <c r="G30" s="4">
+        <v>85.5</v>
       </c>
       <c r="H30">
-        <v>31.9</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B31" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" t="s">
-        <v>25</v>
-      </c>
-      <c r="D31">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="E31">
-        <v>9.9</v>
-      </c>
-      <c r="F31">
-        <v>60.4</v>
-      </c>
-      <c r="G31" s="4">
-        <v>85.5</v>
-      </c>
-      <c r="H31">
         <v>95.9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H31" xr:uid="{25C3A135-87E2-4A5E-8E06-586A6DE8385B}"/>
+  <autoFilter ref="B1:H30" xr:uid="{25C3A135-87E2-4A5E-8E06-586A6DE8385B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4365,527 +4408,8 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A172548-7AE6-4D06-8BBB-21FD94D2FF8B}">
-  <dimension ref="B2:Q26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.1796875" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="14.453125" customWidth="1"/>
-    <col min="7" max="7" width="17.1796875" customWidth="1"/>
-    <col min="8" max="8" width="13.36328125" customWidth="1"/>
-    <col min="12" max="12" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B2" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="L2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N2" t="s">
-        <v>40</v>
-      </c>
-      <c r="O2" s="12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="4">
-        <v>98.5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="4">
-        <v>83.4</v>
-      </c>
-      <c r="K3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3">
-        <v>3</v>
-      </c>
-      <c r="O3" s="12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="4">
-        <v>96.8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="4">
-        <v>84.7</v>
-      </c>
-      <c r="K4" t="s">
-        <v>43</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-      <c r="N4">
-        <v>2</v>
-      </c>
-      <c r="O4" s="12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="4">
-        <v>76.7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="4">
-        <v>46</v>
-      </c>
-      <c r="K5" t="s">
-        <v>44</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>3</v>
-      </c>
-      <c r="O5" s="12">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="4">
-        <v>83.9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="4">
-        <v>60.3</v>
-      </c>
-      <c r="K6" t="s">
-        <v>45</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6">
-        <v>1</v>
-      </c>
-      <c r="O6" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="4">
-        <v>70</v>
-      </c>
-      <c r="F7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="4">
-        <v>99</v>
-      </c>
-      <c r="K7" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>5</v>
-      </c>
-      <c r="O7" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="4">
-        <v>57.9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="4">
-        <v>95.8</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="L8" s="11">
-        <v>10</v>
-      </c>
-      <c r="M8" s="11">
-        <v>5</v>
-      </c>
-      <c r="N8" s="11">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="2:17" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B11" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="K11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L11" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-    </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="4">
-        <v>86</v>
-      </c>
-      <c r="F12" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="4">
-        <v>96.9</v>
-      </c>
-      <c r="K12" t="s">
-        <v>50</v>
-      </c>
-      <c r="L12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="4">
-        <v>74.900000000000006</v>
-      </c>
-      <c r="F13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="4">
-        <v>43.9</v>
-      </c>
-      <c r="L13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="4">
-        <v>64.900000000000006</v>
-      </c>
-      <c r="F14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="4">
-        <v>89.1</v>
-      </c>
-      <c r="L14" s="18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="4">
-        <v>73.3</v>
-      </c>
-      <c r="F15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H15" s="4">
-        <v>76.400000000000006</v>
-      </c>
-      <c r="L15" t="s">
-        <v>59</v>
-      </c>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-    </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="4">
-        <v>95.3</v>
-      </c>
-      <c r="K16" t="s">
-        <v>54</v>
-      </c>
-      <c r="L16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="4">
-        <v>91</v>
-      </c>
-      <c r="K17" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="L17" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-    </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="4">
-        <v>87.1</v>
-      </c>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="4">
-        <v>54.9</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B21" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22" s="4">
-        <v>95.9</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B23" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="4">
-        <v>91.7</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B24" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="4">
-        <v>63.8</v>
-      </c>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="4">
-        <v>53.5</v>
-      </c>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B26" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" s="4">
-        <v>31.9</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="L11:Q11"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86D0E5D6-7A76-4E6F-A0DD-59D4DB683A8B}">
-  <dimension ref="B2:T50"/>
+  <dimension ref="B2:T31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.6328125" customWidth="1"/>
@@ -5233,183 +4757,1381 @@
         <v>54.9</v>
       </c>
     </row>
-    <row r="35" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="F35" t="s">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="F16" t="s">
         <v>39</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G16" t="s">
         <v>41</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H16" t="s">
         <v>40</v>
       </c>
-      <c r="I35" s="12" t="s">
+      <c r="I16" s="12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="E36" t="s">
+    <row r="17" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E17" t="s">
         <v>42</v>
       </c>
-      <c r="F36">
+      <c r="F17">
         <v>2</v>
       </c>
-      <c r="G36">
+      <c r="G17">
         <v>1</v>
       </c>
-      <c r="H36">
+      <c r="H17">
         <v>3</v>
       </c>
-      <c r="I36" s="12">
+      <c r="I17" s="12">
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="E37" t="s">
+    <row r="18" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E18" t="s">
         <v>43</v>
       </c>
-      <c r="F37">
+      <c r="F18">
         <v>2</v>
       </c>
-      <c r="G37">
+      <c r="G18">
         <v>2</v>
       </c>
-      <c r="H37">
+      <c r="H18">
         <v>2</v>
       </c>
-      <c r="I37" s="12">
+      <c r="I18" s="12">
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="E38" t="s">
+    <row r="19" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E19" t="s">
         <v>44</v>
       </c>
-      <c r="F38">
+      <c r="F19">
         <v>4</v>
       </c>
-      <c r="G38">
+      <c r="G19">
         <v>1</v>
       </c>
-      <c r="H38">
+      <c r="H19">
         <v>3</v>
       </c>
-      <c r="I38" s="12">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="E39" t="s">
+      <c r="I19" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E20" t="s">
         <v>45</v>
       </c>
-      <c r="F39">
+      <c r="F20">
         <v>2</v>
       </c>
-      <c r="G39">
+      <c r="G20">
         <v>1</v>
       </c>
-      <c r="H39">
+      <c r="H20">
         <v>1</v>
       </c>
-      <c r="I39" s="12">
+      <c r="I20" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="E40" t="s">
+    <row r="21" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E21" t="s">
         <v>46</v>
       </c>
-      <c r="F40">
+      <c r="F21">
         <v>0</v>
       </c>
-      <c r="G40">
+      <c r="G21">
         <v>0</v>
       </c>
-      <c r="H40">
+      <c r="H21">
         <v>5</v>
       </c>
-      <c r="I40" s="12">
+      <c r="I21" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="5:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E41" s="11" t="s">
+    <row r="22" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E22" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F41" s="11">
+      <c r="F22" s="11">
         <v>10</v>
       </c>
-      <c r="G41" s="11">
+      <c r="G22" s="11">
         <v>5</v>
       </c>
-      <c r="H41" s="11">
+      <c r="H22" s="11">
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="5:11" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
-    <row r="44" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="E44" t="s">
+    <row r="23" spans="5:13" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
+    <row r="25" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E25" t="s">
         <v>49</v>
       </c>
-      <c r="F44" s="23" t="s">
+      <c r="F25" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="G44" s="23"/>
-      <c r="H44" s="23"/>
-      <c r="I44" s="23"/>
-      <c r="J44" s="23"/>
-      <c r="K44" s="23"/>
-    </row>
-    <row r="45" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="E45" t="s">
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+    </row>
+    <row r="26" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E26" t="s">
         <v>50</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F26" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="F46" t="s">
+    <row r="27" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="F27" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="47" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="F47" s="18" t="s">
+      <c r="M27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="F28" s="18" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="F48" t="s">
+    <row r="29" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="F29" t="s">
         <v>59</v>
       </c>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-    </row>
-    <row r="49" spans="5:9" x14ac:dyDescent="0.35">
-      <c r="E49" t="s">
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+    </row>
+    <row r="30" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E30" t="s">
         <v>54</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F30" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="50" spans="5:9" x14ac:dyDescent="0.35">
-      <c r="E50" s="13" t="s">
+    <row r="31" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E31" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="F50" s="13" t="s">
+      <c r="F31" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="F44:K44"/>
+    <mergeCell ref="F25:K25"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA088233-5EF0-45F9-8BF7-5534FE391935}">
+  <dimension ref="B2:T73"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="4.6328125" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.36328125" customWidth="1"/>
+    <col min="6" max="6" width="14.453125" customWidth="1"/>
+    <col min="7" max="7" width="17.1796875" customWidth="1"/>
+    <col min="8" max="8" width="13.90625" customWidth="1"/>
+    <col min="9" max="9" width="4.6328125" customWidth="1"/>
+    <col min="11" max="11" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.453125" customWidth="1"/>
+    <col min="14" max="14" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.6328125" customWidth="1"/>
+    <col min="18" max="18" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B2" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B4" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="O4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="P4" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="R4" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="S4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="26">
+        <v>83.9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="26">
+        <v>99</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="26">
+        <v>86</v>
+      </c>
+      <c r="N5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P5" s="26">
+        <v>96.9</v>
+      </c>
+      <c r="R5" t="s">
+        <v>31</v>
+      </c>
+      <c r="S5" t="s">
+        <v>25</v>
+      </c>
+      <c r="T5" s="26">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="26">
+        <v>70</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="28">
+        <v>95.8</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="26">
+        <v>48.1</v>
+      </c>
+      <c r="N6" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="O6" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="P6" s="26">
+        <v>85.5</v>
+      </c>
+      <c r="R6" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="S6" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="T6" s="26">
+        <v>90.3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="26">
+        <v>76.7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="26">
+        <v>93.3</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" s="26">
+        <v>73.3</v>
+      </c>
+      <c r="N7" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="O7" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="P7" s="26">
+        <v>84.3</v>
+      </c>
+      <c r="R7" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="S7" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="T7" s="28">
+        <v>84.7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="26">
+        <v>98.5</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="26">
+        <v>77.599999999999994</v>
+      </c>
+      <c r="J8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="26">
+        <v>95.3</v>
+      </c>
+      <c r="N8" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="O8" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="P8" s="26">
+        <v>70.5</v>
+      </c>
+      <c r="R8" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="S8" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="T8" s="28">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="26">
+        <v>96.8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="26">
+        <v>84.7</v>
+      </c>
+      <c r="J9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="26">
+        <v>91</v>
+      </c>
+      <c r="N9" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="O9" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="P9" s="26">
+        <v>63.4</v>
+      </c>
+      <c r="R9" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="S9" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="T9" s="26">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="J10" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="26">
+        <v>87.1</v>
+      </c>
+      <c r="N10" t="s">
+        <v>17</v>
+      </c>
+      <c r="O10" t="s">
+        <v>8</v>
+      </c>
+      <c r="P10" s="26">
+        <v>89.1</v>
+      </c>
+      <c r="R10" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="S10" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="T10" s="26">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="24"/>
+      <c r="N11" t="s">
+        <v>14</v>
+      </c>
+      <c r="O11" t="s">
+        <v>8</v>
+      </c>
+      <c r="P11" s="26">
+        <v>76.400000000000006</v>
+      </c>
+      <c r="R11" s="24"/>
+      <c r="S11" s="24"/>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
+      <c r="P12" s="29"/>
+      <c r="R12" s="24"/>
+      <c r="S12" s="24"/>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B15" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="O15" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="P15" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="S15" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="T15" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="29">
+        <v>83.9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="29">
+        <v>99</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" s="29">
+        <v>86</v>
+      </c>
+      <c r="M16" s="30"/>
+      <c r="N16" t="s">
+        <v>28</v>
+      </c>
+      <c r="O16" t="s">
+        <v>25</v>
+      </c>
+      <c r="P16" s="29">
+        <v>96.9</v>
+      </c>
+      <c r="R16" t="s">
+        <v>31</v>
+      </c>
+      <c r="S16" t="s">
+        <v>25</v>
+      </c>
+      <c r="T16" s="29">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="29">
+        <v>70</v>
+      </c>
+      <c r="F17" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="32">
+        <v>95.8</v>
+      </c>
+      <c r="I17" s="1"/>
+      <c r="J17" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="29">
+        <v>48.1</v>
+      </c>
+      <c r="M17" s="30"/>
+      <c r="N17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="O17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P17" s="31">
+        <v>85.5</v>
+      </c>
+      <c r="R17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="S17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="T17" s="31">
+        <v>90.3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="29">
+        <v>76.7</v>
+      </c>
+      <c r="F18" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="29">
+        <v>93.3</v>
+      </c>
+      <c r="I18" s="1"/>
+      <c r="J18" t="s">
+        <v>23</v>
+      </c>
+      <c r="K18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L18" s="29">
+        <v>73.3</v>
+      </c>
+      <c r="M18" s="30"/>
+      <c r="N18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="O18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P18" s="31">
+        <v>84.3</v>
+      </c>
+      <c r="R18" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="S18" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="T18" s="35">
+        <v>84.7</v>
+      </c>
+    </row>
+    <row r="19" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="29">
+        <v>98.5</v>
+      </c>
+      <c r="F19" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="31">
+        <v>77.599999999999994</v>
+      </c>
+      <c r="J19" t="s">
+        <v>10</v>
+      </c>
+      <c r="K19" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="29">
+        <v>95.3</v>
+      </c>
+      <c r="M19" s="30"/>
+      <c r="N19" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P19" s="31">
+        <v>70.5</v>
+      </c>
+      <c r="R19" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="S19" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="T19" s="35">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="29">
+        <v>96.8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="29">
+        <v>84.7</v>
+      </c>
+      <c r="J20" t="s">
+        <v>9</v>
+      </c>
+      <c r="K20" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="29">
+        <v>91</v>
+      </c>
+      <c r="M20" s="30"/>
+      <c r="N20" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="O20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P20" s="31">
+        <v>63.4</v>
+      </c>
+      <c r="R20" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="S20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="T20" s="31">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B21" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="24"/>
+      <c r="F21" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G21" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="H21" s="24"/>
+      <c r="J21" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="29">
+        <v>87.1</v>
+      </c>
+      <c r="N21" t="s">
+        <v>17</v>
+      </c>
+      <c r="O21" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="29">
+        <v>89.1</v>
+      </c>
+      <c r="R21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="S21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="T21" s="31">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="F22" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G22" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="J22" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="K22" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="L22" s="24"/>
+      <c r="N22" t="s">
+        <v>14</v>
+      </c>
+      <c r="O22" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="29">
+        <v>76.400000000000006</v>
+      </c>
+      <c r="R22" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="S22" s="25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="F23" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G23" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="J23" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="L23" s="24"/>
+      <c r="N23" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="O23" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="P23" s="24"/>
+      <c r="R23" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="S23" s="25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+      <c r="P24" s="24"/>
+      <c r="R24" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="S24" s="25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="J25" s="24"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="R25" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="S25" s="25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="J26" s="24"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="24"/>
+      <c r="P26" s="24"/>
+      <c r="R26" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="S26" s="25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B27" s="1"/>
+      <c r="F27" s="37"/>
+      <c r="J27" s="24"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="24"/>
+      <c r="P27" s="24"/>
+    </row>
+    <row r="28" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="J28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+      <c r="P28" s="24"/>
+    </row>
+    <row r="29" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="J29" s="24"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+      <c r="P29" s="24"/>
+    </row>
+    <row r="30" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B30" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J30" s="24"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="24"/>
+      <c r="P30" s="24"/>
+    </row>
+    <row r="31" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31">
+        <v>15.6</v>
+      </c>
+      <c r="E31" s="4">
+        <v>77.599999999999994</v>
+      </c>
+      <c r="F31">
+        <v>24.3</v>
+      </c>
+      <c r="G31">
+        <v>5.3</v>
+      </c>
+      <c r="H31">
+        <v>53.5</v>
+      </c>
+      <c r="J31" s="24"/>
+      <c r="K31" s="24"/>
+      <c r="L31" s="24"/>
+      <c r="P31" s="24"/>
+    </row>
+    <row r="32" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="J32" s="24"/>
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+      <c r="P32" s="24"/>
+    </row>
+    <row r="33" spans="10:16" x14ac:dyDescent="0.35">
+      <c r="J33" s="24"/>
+      <c r="K33" s="24"/>
+      <c r="L33" s="24"/>
+      <c r="P33" s="24"/>
+    </row>
+    <row r="34" spans="10:16" x14ac:dyDescent="0.35">
+      <c r="J34" s="24"/>
+      <c r="K34" s="24"/>
+      <c r="L34" s="24"/>
+      <c r="P34" s="24"/>
+    </row>
+    <row r="35" spans="10:16" x14ac:dyDescent="0.35">
+      <c r="J35" s="24"/>
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
+      <c r="P35" s="24"/>
+    </row>
+    <row r="36" spans="10:16" x14ac:dyDescent="0.35">
+      <c r="J36" s="24"/>
+      <c r="K36" s="24"/>
+      <c r="L36" s="24"/>
+      <c r="P36" s="24"/>
+    </row>
+    <row r="37" spans="10:16" x14ac:dyDescent="0.35">
+      <c r="J37" s="24"/>
+      <c r="K37" s="24"/>
+      <c r="L37" s="24"/>
+      <c r="P37" s="24"/>
+    </row>
+    <row r="38" spans="10:16" x14ac:dyDescent="0.35">
+      <c r="J38" s="24"/>
+      <c r="K38" s="24"/>
+      <c r="L38" s="24"/>
+      <c r="P38" s="24"/>
+    </row>
+    <row r="39" spans="10:16" x14ac:dyDescent="0.35">
+      <c r="J39" s="24"/>
+      <c r="K39" s="24"/>
+      <c r="L39" s="24"/>
+      <c r="P39" s="24"/>
+    </row>
+    <row r="40" spans="10:16" x14ac:dyDescent="0.35">
+      <c r="J40" s="24"/>
+      <c r="K40" s="24"/>
+      <c r="L40" s="24"/>
+      <c r="P40" s="24"/>
+    </row>
+    <row r="41" spans="10:16" x14ac:dyDescent="0.35">
+      <c r="J41" s="24"/>
+      <c r="K41" s="24"/>
+      <c r="L41" s="24"/>
+      <c r="P41" s="24"/>
+    </row>
+    <row r="42" spans="10:16" x14ac:dyDescent="0.35">
+      <c r="J42" s="24"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="P42" s="24"/>
+    </row>
+    <row r="43" spans="10:16" x14ac:dyDescent="0.35">
+      <c r="J43" s="24"/>
+      <c r="K43" s="24"/>
+      <c r="L43" s="24"/>
+      <c r="P43" s="24"/>
+    </row>
+    <row r="44" spans="10:16" x14ac:dyDescent="0.35">
+      <c r="J44" s="24"/>
+      <c r="K44" s="24"/>
+      <c r="L44" s="24"/>
+      <c r="P44" s="24"/>
+    </row>
+    <row r="45" spans="10:16" x14ac:dyDescent="0.35">
+      <c r="J45" s="24"/>
+      <c r="K45" s="24"/>
+      <c r="L45" s="24"/>
+      <c r="P45" s="24"/>
+    </row>
+    <row r="46" spans="10:16" x14ac:dyDescent="0.35">
+      <c r="J46" s="24"/>
+      <c r="K46" s="24"/>
+      <c r="L46" s="24"/>
+      <c r="P46" s="24"/>
+    </row>
+    <row r="47" spans="10:16" x14ac:dyDescent="0.35">
+      <c r="J47" s="24"/>
+      <c r="K47" s="24"/>
+      <c r="L47" s="24"/>
+      <c r="P47" s="24"/>
+    </row>
+    <row r="48" spans="10:16" x14ac:dyDescent="0.35">
+      <c r="J48" s="24"/>
+      <c r="K48" s="24"/>
+      <c r="L48" s="24"/>
+      <c r="P48" s="24"/>
+    </row>
+    <row r="49" spans="6:16" x14ac:dyDescent="0.35">
+      <c r="J49" s="24"/>
+      <c r="K49" s="24"/>
+      <c r="L49" s="24"/>
+      <c r="P49" s="24"/>
+    </row>
+    <row r="50" spans="6:16" x14ac:dyDescent="0.35">
+      <c r="G50" t="s">
+        <v>39</v>
+      </c>
+      <c r="H50" t="s">
+        <v>41</v>
+      </c>
+      <c r="I50" t="s">
+        <v>40</v>
+      </c>
+      <c r="J50" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K50" s="24"/>
+      <c r="L50" s="24"/>
+      <c r="P50" s="24"/>
+    </row>
+    <row r="51" spans="6:16" x14ac:dyDescent="0.35">
+      <c r="F51" t="s">
+        <v>42</v>
+      </c>
+      <c r="G51">
+        <v>2</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51" s="25">
+        <v>3</v>
+      </c>
+      <c r="J51" s="12">
+        <v>6</v>
+      </c>
+      <c r="K51" s="24"/>
+      <c r="L51" s="24"/>
+      <c r="P51" s="24"/>
+    </row>
+    <row r="52" spans="6:16" x14ac:dyDescent="0.35">
+      <c r="F52" t="s">
+        <v>43</v>
+      </c>
+      <c r="G52">
+        <v>2</v>
+      </c>
+      <c r="H52" s="25">
+        <v>2</v>
+      </c>
+      <c r="I52" s="25">
+        <v>2</v>
+      </c>
+      <c r="J52" s="12">
+        <v>6</v>
+      </c>
+      <c r="K52" s="24"/>
+      <c r="L52" s="24"/>
+    </row>
+    <row r="53" spans="6:16" x14ac:dyDescent="0.35">
+      <c r="F53" t="s">
+        <v>44</v>
+      </c>
+      <c r="G53" s="25">
+        <v>4</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
+      </c>
+      <c r="I53" s="25">
+        <v>3</v>
+      </c>
+      <c r="J53" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="6:16" x14ac:dyDescent="0.35">
+      <c r="F54" t="s">
+        <v>45</v>
+      </c>
+      <c r="G54">
+        <v>2</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+      <c r="J54" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="6:16" x14ac:dyDescent="0.35">
+      <c r="F55" t="s">
+        <v>46</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>5</v>
+      </c>
+      <c r="J55" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="6:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F56" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G56" s="11">
+        <v>10</v>
+      </c>
+      <c r="H56" s="11">
+        <v>5</v>
+      </c>
+      <c r="I56" s="11">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="6:16" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
+    <row r="67" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E67" t="s">
+        <v>49</v>
+      </c>
+      <c r="F67" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="G67" s="23"/>
+      <c r="H67" s="23"/>
+      <c r="I67" s="23"/>
+      <c r="J67" s="23"/>
+      <c r="K67" s="23"/>
+    </row>
+    <row r="68" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E68" t="s">
+        <v>50</v>
+      </c>
+      <c r="F68" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="69" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="F69" t="s">
+        <v>52</v>
+      </c>
+      <c r="M69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="F70" s="18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="71" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="F71" t="s">
+        <v>59</v>
+      </c>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1"/>
+    </row>
+    <row r="72" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E72" t="s">
+        <v>54</v>
+      </c>
+      <c r="F72" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="73" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E73" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="F73" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G73" s="13"/>
+      <c r="H73" s="13"/>
+      <c r="I73" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F67:K67"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="F18" location="'Stage 1'!A1" display="VP6" xr:uid="{11E86EC5-B611-4BFA-BA48-BEFD10AC62C8}"/>
+    <hyperlink ref="F19" location="'Stage 1'!A1" display="VP7" xr:uid="{CC8CB78E-623A-44BF-98AC-AF14F818CE53}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/1.training_model/supplementary/Data Tabulation - Flowchart.xlsx
+++ b/1.training_model/supplementary/Data Tabulation - Flowchart.xlsx
@@ -8,27 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sitisyaziyah\source\repos\DeviceCluster\1.training_model\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A10780F-3F7D-46DD-A140-9ABCD75F2469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB49188-21D2-4489-AB27-5A04AD39C6EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="717" activeTab="5" xr2:uid="{E471D6E3-533D-4285-ABDC-6FF3DFDEE99D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="717" xr2:uid="{E471D6E3-533D-4285-ABDC-6FF3DFDEE99D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Cluster INFO" sheetId="11" r:id="rId1"/>
-    <sheet name="Stage 1" sheetId="4" r:id="rId2"/>
-    <sheet name="Stage 2" sheetId="6" r:id="rId3"/>
-    <sheet name="Stage 3" sheetId="7" r:id="rId4"/>
-    <sheet name="Stage 4" sheetId="13" r:id="rId5"/>
-    <sheet name="draft" sheetId="15" r:id="rId6"/>
-    <sheet name="Example case" sheetId="12" r:id="rId7"/>
-    <sheet name="transpose" sheetId="3" state="hidden" r:id="rId8"/>
+    <sheet name="Overview" sheetId="17" r:id="rId1"/>
+    <sheet name="flowchart" sheetId="12" r:id="rId2"/>
+    <sheet name="Cluster Info" sheetId="16" r:id="rId3"/>
+    <sheet name="Stage 1" sheetId="4" r:id="rId4"/>
+    <sheet name="Stage 2" sheetId="6" r:id="rId5"/>
+    <sheet name="Stage 3" sheetId="7" r:id="rId6"/>
+    <sheet name="Stage 4" sheetId="13" r:id="rId7"/>
+    <sheet name="DRAFT" sheetId="15" r:id="rId8"/>
+    <sheet name="Sheet2" sheetId="18" r:id="rId9"/>
+    <sheet name="transpose" sheetId="3" state="hidden" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">draft!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Stage 1'!$B$1:$H$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Stage 2'!$B$2:$H$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stage 3'!$B$2:$H$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Stage 4'!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">transpose!$B$3:$AE$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">DRAFT!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stage 1'!$B$1:$H$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Stage 2'!$B$2:$H$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Stage 3'!$B$2:$H$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Stage 4'!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">transpose!$B$3:$AE$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="86">
   <si>
     <t>Device ID</t>
   </si>
@@ -253,12 +255,69 @@
   <si>
     <t>Check the vacant and extra</t>
   </si>
+  <si>
+    <t>Kick out the lowest per Device ID</t>
+  </si>
+  <si>
+    <t>STAGE 5</t>
+  </si>
+  <si>
+    <t>Insert the removal Device ID into DUMP group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLUSTER </t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>STAGE 6</t>
+  </si>
+  <si>
+    <t>STAGE 7</t>
+  </si>
+  <si>
+    <t>Re-evaluate the DEVICE_ID using the Next Highest Percentage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2nd HIGHEST CLUSTER </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3rd HIGHEST CLUSTER </t>
+  </si>
+  <si>
+    <t>Grouping DEVICE ID into respective CLUSTER</t>
+  </si>
+  <si>
+    <t>[BLANK]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">formation pattern CLUSTER </t>
+  </si>
+  <si>
+    <t>Mark the highest prediction %</t>
+  </si>
+  <si>
+    <t>DUMP GROUP</t>
+  </si>
+  <si>
+    <t>HOW TO FILL?</t>
+  </si>
+  <si>
+    <t>Kick out the lowest %</t>
+  </si>
+  <si>
+    <t>Move into DUMP Group</t>
+  </si>
+  <si>
+    <t>(the percentage is obtain from the prediction)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -290,8 +349,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -340,8 +427,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC9C9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -380,12 +497,157 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -423,24 +685,74 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="13" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="14" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -448,6 +760,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFC9C9"/>
+      <color rgb="FFFF9B9B"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -463,14 +781,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>485589</xdr:colOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>495086</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>140157</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>146685</xdr:colOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>156182</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>118567</xdr:rowOff>
     </xdr:to>
@@ -479,7 +797,7 @@
         <xdr:cNvPr id="2" name="Rectangle 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79ACE8BA-C2C4-4696-98BE-AA0855AB6578}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DA57138-72EE-4C32-B2C3-8E5987647994}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -487,8 +805,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6722276" y="1412401"/>
-          <a:ext cx="2097881" cy="543852"/>
+          <a:off x="13296686" y="1410157"/>
+          <a:ext cx="2102671" cy="521335"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -540,23 +858,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>143510</xdr:colOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>156182</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>33060</xdr:rowOff>
+      <xdr:rowOff>38648</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>354708</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>41663</xdr:rowOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>425996</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>4294</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="3" name="Straight Arrow Connector 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08CBFA1D-BCA7-48CA-AC5D-35E90DB26ADA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51627219-8552-445C-9FC8-46FD249ABD25}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -566,9 +884,9 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="8816982" y="1678899"/>
-          <a:ext cx="2647982" cy="8603"/>
+        <a:xfrm>
+          <a:off x="15399357" y="1667423"/>
+          <a:ext cx="2708214" cy="330771"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -596,23 +914,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>357883</xdr:colOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>425996</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>99301</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>569386</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>142216</xdr:rowOff>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>34248</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>90714</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="4" name="Rectangle 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9369CE89-687B-49E4-8342-6C958772E9D2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F51C920-A03E-474F-BE52-E7367095D36B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -620,8 +938,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11468139" y="1371545"/>
-          <a:ext cx="2039092" cy="608357"/>
+          <a:off x="18107571" y="1369301"/>
+          <a:ext cx="2040302" cy="1251888"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -677,35 +995,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>316137</xdr:colOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>391721</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>102476</xdr:rowOff>
+      <xdr:rowOff>80065</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>157450</xdr:colOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>233034</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>143332</xdr:rowOff>
+      <xdr:rowOff>120921</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="5" name="Connector: Elbow 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60A86750-00DA-4846-BA68-12F84645B061}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF7DE1ED-635D-47AE-9B49-6BF0912F6E9A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="4" idx="0"/>
-          <a:endCxn id="2" idx="0"/>
-        </xdr:cNvCxnSpPr>
+        <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000" flipH="1" flipV="1">
-          <a:off x="10108230" y="-962293"/>
-          <a:ext cx="40856" cy="4714881"/>
+          <a:off x="16751150" y="-991739"/>
+          <a:ext cx="40856" cy="4724463"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
@@ -735,23 +1050,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>392025</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>544640</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>44823</xdr:rowOff>
+      <xdr:rowOff>16008</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>491939</xdr:colOff>
+      <xdr:colOff>31965</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>119528</xdr:rowOff>
+      <xdr:rowOff>145143</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="Rectangle 12">
+        <xdr:cNvPr id="6" name="Rectangle 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06521A89-507B-4D0E-9B04-34C37F7742BB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FECA9D57-FFB0-46A2-BAAC-2EAE9562C7C8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -759,8 +1074,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6644907" y="418352"/>
-          <a:ext cx="1937679" cy="448235"/>
+          <a:off x="1151065" y="377958"/>
+          <a:ext cx="1925725" cy="487910"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -816,34 +1131,35 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>136388</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>288303</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>119528</xdr:rowOff>
+      <xdr:rowOff>145143</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>111125</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>294124</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>158392</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="48" name="Straight Arrow Connector 47">
+        <xdr:cNvPr id="7" name="Straight Arrow Connector 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A0E8AF7-1469-4CF8-9270-E410FC37A4DA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BAA1E64-925E-4CAC-BC28-3179C0BE504C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="13" idx="2"/>
+          <a:stCxn id="6" idx="2"/>
+          <a:endCxn id="15" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7605576" y="849778"/>
-          <a:ext cx="6487" cy="539285"/>
+          <a:off x="2117103" y="865868"/>
+          <a:ext cx="8996" cy="381549"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -871,23 +1187,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>216640</xdr:colOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>314634</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>164766</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>381740</xdr:colOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>479734</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>108941</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="51" name="Rectangle 50">
+        <xdr:cNvPr id="8" name="Rectangle 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A763027F-400C-4FBE-AF68-A653018E8F8A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD0F8981-E002-4534-9E5E-ABC90DC9CB02}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -895,8 +1211,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6450449" y="2552096"/>
-          <a:ext cx="2597014" cy="308962"/>
+          <a:off x="13113059" y="2514266"/>
+          <a:ext cx="2609850" cy="306125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -948,35 +1264,35 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>300778</xdr:colOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>325634</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>121742</xdr:rowOff>
+      <xdr:rowOff>118567</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>316137</xdr:colOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>397184</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>161591</xdr:rowOff>
+      <xdr:rowOff>164766</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="52" name="Straight Arrow Connector 51">
+        <xdr:cNvPr id="9" name="Straight Arrow Connector 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22ADB756-6784-47BD-A77E-F5171818F4E5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C22A4850-55F6-4D3E-AD5D-5EEC0161A8AE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="2" idx="2"/>
-          <a:endCxn id="51" idx="0"/>
+          <a:endCxn id="8" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="7750544" y="1961891"/>
-          <a:ext cx="15359" cy="587030"/>
+        <a:xfrm>
+          <a:off x="14346434" y="1931492"/>
+          <a:ext cx="71550" cy="582774"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1004,18 +1320,18 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>257159</xdr:colOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>198968</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>73269</xdr:rowOff>
+      <xdr:rowOff>145263</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="385105" cy="264560"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="57" name="TextBox 56">
+        <xdr:cNvPr id="10" name="TextBox 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD290980-AA0F-DF20-3370-5A2CF1C521C2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FC934D5-5071-4E4E-BF59-5E840B58CD67}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1023,7 +1339,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8960394" y="1380622"/>
+          <a:off x="16661343" y="1408913"/>
           <a:ext cx="385105" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1062,18 +1378,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>587666</xdr:colOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>48386</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>156978</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="346826" cy="264560"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="58" name="TextBox 57">
+        <xdr:cNvPr id="11" name="TextBox 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A08F5406-DF08-177D-0B5D-9D30975E467E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{127CBB58-98D8-472F-921F-47CB20313BDD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1081,7 +1397,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7429453" y="2179521"/>
+          <a:off x="14066011" y="2150878"/>
           <a:ext cx="346826" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1120,23 +1436,23 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>213246</xdr:colOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>311240</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>153045</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>384555</xdr:colOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>482549</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>47126</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="60" name="Rectangle 59">
+        <xdr:cNvPr id="12" name="Rectangle 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E1654B4-37CD-4AB5-A461-58695B014FAA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0BB6DE7-D2EB-43EF-BBE2-630AE4C5CD3D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1144,8 +1460,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6447055" y="3269949"/>
-          <a:ext cx="2603223" cy="441262"/>
+          <a:off x="13116015" y="3229620"/>
+          <a:ext cx="2609709" cy="440181"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1197,35 +1513,35 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>300778</xdr:colOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>396895</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>105766</xdr:rowOff>
+      <xdr:rowOff>108941</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>302076</xdr:colOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>397184</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>153045</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="61" name="Straight Arrow Connector 60">
+        <xdr:cNvPr id="13" name="Straight Arrow Connector 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{015DDCA4-98B6-4F9E-A796-F10DD97430BB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0899900E-20F7-401B-8E97-8B2066AF638D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="51" idx="2"/>
-          <a:endCxn id="60" idx="0"/>
+          <a:stCxn id="8" idx="2"/>
+          <a:endCxn id="12" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7750544" y="2857883"/>
-          <a:ext cx="1298" cy="412066"/>
+        <a:xfrm flipH="1">
+          <a:off x="14417695" y="2820391"/>
+          <a:ext cx="289" cy="409229"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1253,23 +1569,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>146685</xdr:colOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>156182</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>34222</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>190203</xdr:colOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>199701</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>128311</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="8" name="Straight Arrow Connector 7">
+        <xdr:cNvPr id="14" name="Straight Arrow Connector 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1EFB6FF-5D50-4445-8AC9-D9B27502E62A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0675A1F-A543-44D2-AB71-608C9C0A4F2A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1279,8 +1595,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8820157" y="1680061"/>
-          <a:ext cx="2480302" cy="1376430"/>
+          <a:off x="15399357" y="1659822"/>
+          <a:ext cx="2481919" cy="1360914"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1297,6 +1613,2117 @@
           <a:schemeClr val="accent1"/>
         </a:fillRef>
         <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>135374</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>158392</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>452873</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>108857</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Rectangle 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69CF27E6-82DB-4E1F-ABE8-105C19522AF0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="744974" y="1247417"/>
+          <a:ext cx="2752724" cy="487040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="90000"/>
+            <a:lumOff val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100"/>
+            <a:t>Stage</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t> 2 : </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Grouping DEVICE ID into respective CLUSTER</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>237794</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>167743</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>354047</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>110153</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="Rectangle 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{288F1BBF-B2FF-4B94-BD36-044CF6A17C74}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1460169" y="2155293"/>
+          <a:ext cx="1329103" cy="485335"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="90000"/>
+            <a:lumOff val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100"/>
+            <a:t>Stage</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t> 3 : </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Check the CLUSTER</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>294124</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>108857</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>295921</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>167743</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="Straight Arrow Connector 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41BF338D-9667-484E-87A9-DE0CA4AF9C0B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="15" idx="2"/>
+          <a:endCxn id="16" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2126099" y="1734457"/>
+          <a:ext cx="0" cy="420836"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>354047</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>48234</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>371938</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>60305</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="18" name="Straight Arrow Connector 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7610ED5D-1D89-49E3-AC82-D812A66A4BE3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="16" idx="3"/>
+          <a:endCxn id="22" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2789272" y="2397734"/>
+          <a:ext cx="1846691" cy="15246"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>572123</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>143726</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1004699" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="TextBox 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42FC8260-05D7-462D-96E8-050BC52AA65E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3010523" y="2131276"/>
+          <a:ext cx="1004699" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100"/>
+            <a:t>Cluster =</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" baseline="0"/>
+            <a:t> FULL</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>83073</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>165701</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1114023" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="TextBox 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E9C2376-9611-422F-BEDA-D6C5E1321BEE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3146014" y="2220113"/>
+          <a:ext cx="1114023" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100"/>
+            <a:t>Cluster =</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" baseline="0"/>
+            <a:t> Vacant</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>545727</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>7471</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>552795</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>37354</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="21" name="Straight Arrow Connector 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{170FABAE-EF0B-4B00-8519-5101DD47D2D4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="31" idx="2"/>
+          <a:endCxn id="54" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1770903" y="2622177"/>
+          <a:ext cx="7068" cy="590177"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>371938</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>21967</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>540398</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>98641</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="Rectangle 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{471B206C-FB6B-4030-9BB1-5B3B3CD4B4EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4635963" y="2193667"/>
+          <a:ext cx="2613210" cy="441799"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="90000"/>
+            <a:lumOff val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100"/>
+            <a:t>Stage</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t> 4 : </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Evaluate DEVICE ID percentage prediction</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>47733</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>170389</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>412750</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>89025</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="Rectangle 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E80A0535-438A-4DFA-98B9-07E0870C459C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6750158" y="3246964"/>
+          <a:ext cx="2803417" cy="458386"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="90000"/>
+            <a:lumOff val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100"/>
+            <a:t>Stage </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>5: </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Kick out the lowest percentage per Device</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> Type </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>456168</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>98641</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>230242</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>170389</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="24" name="Straight Arrow Connector 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CE3B474-B887-4AD8-BC49-E6CF666DE675}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="22" idx="2"/>
+          <a:endCxn id="23" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5942568" y="2635466"/>
+          <a:ext cx="2212474" cy="611498"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>349537</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>98641</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>456168</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>170391</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="25" name="Straight Arrow Connector 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D312150-548B-434B-BE0F-E032603EAF6B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="22" idx="2"/>
+          <a:endCxn id="28" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="4619912" y="2635466"/>
+          <a:ext cx="1322656" cy="611500"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>274183</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>2491</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>187808</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>155245</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="Rectangle 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D8A7CDC-4BFC-4252-8E72-F0307A876437}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6982958" y="4164916"/>
+          <a:ext cx="2348850" cy="514704"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="90000"/>
+            <a:lumOff val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>STAGE</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> 6</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Move the Device ID into dump</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> group</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>230242</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>89025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>230996</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>2491</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="27" name="Straight Arrow Connector 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D266DB7-E331-460A-9A92-1F774A1A00CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="23" idx="2"/>
+          <a:endCxn id="26" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8155042" y="3705350"/>
+          <a:ext cx="754" cy="459566"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>185551</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>170391</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>513522</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>93871</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="Rectangle 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FD48E40-4EDC-4DAD-AD40-33159EDDA8A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3230376" y="3246966"/>
+          <a:ext cx="2769546" cy="285430"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="90000"/>
+            <a:lumOff val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>High percentage</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> Device Type </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>remain in cluster</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>276012</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>92688</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>213645</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>178559</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="Rectangle 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D00DE24E-D4C0-4BEE-82A5-5B3C8FD89468}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6375187" y="5159988"/>
+          <a:ext cx="3595233" cy="450996"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="90000"/>
+            <a:lumOff val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>STAGE</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> 7</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY"/>
+            <a:t>Re-evaluate the DEVICE_ID using the Next Highest Percentage</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>230996</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>155245</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>244829</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>92688</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="30" name="Straight Arrow Connector 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3895B373-E2CA-4EA0-A709-0C4A5C219AFC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="26" idx="2"/>
+          <a:endCxn id="29" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8155796" y="4679620"/>
+          <a:ext cx="13833" cy="480368"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>231589</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>92146</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>261411</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>7471</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="Rectangle 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75591000-DEAC-439D-AD16-1507A2E814B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="844177" y="2333322"/>
+          <a:ext cx="1867587" cy="288855"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="90000"/>
+            <a:lumOff val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Fill up from the DUMP Group</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>421367</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>118446</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>215080</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>174113</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="32" name="Connector: Elbow 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC96F8C4-E878-40F9-88FB-496FBBC47D6D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="3493948" y="1593285"/>
+          <a:ext cx="6553390" cy="4664538"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -18921"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>281236</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>8295</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>218869</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>92178</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="Rectangle 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E03F21F-9235-4F89-9E61-9E3129315C41}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6426397" y="6092005"/>
+          <a:ext cx="3624730" cy="268238"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="90000"/>
+            <a:lumOff val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY"/>
+            <a:t>Move the Next Highest Percentage into subsequent</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" baseline="0"/>
+            <a:t> cluster</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>244828</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>178559</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>250052</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>8295</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="42" name="Straight Arrow Connector 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5C55F15-3A99-4904-AE80-6E73B38BFE4B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="29" idx="2"/>
+          <a:endCxn id="39" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8233538" y="5709204"/>
+          <a:ext cx="5224" cy="382801"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>261411</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>45566</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>237794</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>49809</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="46" name="Straight Arrow Connector 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47D5FD08-5A06-4D7A-95AF-FF2E82DDF183}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="16" idx="1"/>
+          <a:endCxn id="31" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2711764" y="2473507"/>
+          <a:ext cx="1814148" cy="4243"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>463176</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>37354</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>15688</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>168294</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="54" name="Rectangle 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CD7836B-749A-4D92-A0F1-3C49472A6CCB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="463176" y="3212354"/>
+          <a:ext cx="2615453" cy="317705"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="90000"/>
+            <a:lumOff val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100"/>
+            <a:t>Assign</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t> Device ID into the respective cluster</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>384082</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>42083</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>99465</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>152327</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="58" name="Rectangle 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8E94DE5-B42B-4877-8EC3-C8A2D42D752F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="384082" y="3964142"/>
+          <a:ext cx="2778324" cy="297009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="90000"/>
+            <a:lumOff val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>High percentage</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> Device Type </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>remain in cluster</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>545727</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>168294</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>548068</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>42083</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="59" name="Straight Arrow Connector 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AD2AB85-3D94-418C-A68D-B65D45BD9848}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="54" idx="2"/>
+          <a:endCxn id="58" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1770903" y="3530059"/>
+          <a:ext cx="2341" cy="434083"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>854076</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>62635</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1601137</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>11838</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="Connector: Elbow 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C90BAFBD-B84C-47FB-B378-BC651347F8AB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="9724483" y="8856774"/>
+          <a:ext cx="1450112" cy="747061"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 100259"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>69850</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>450850</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>14568</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="Connector: Elbow 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEC9654B-97B4-42DC-B105-EA679D3F380D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000" flipH="1" flipV="1">
+          <a:off x="10441641" y="8741709"/>
+          <a:ext cx="1392518" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 264"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>143700</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>92364</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>484909</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>94424</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="Straight Arrow Connector 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00E10537-0C29-36A9-A1FB-DBDFFF793894}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="13028427" y="4387273"/>
+          <a:ext cx="1449573" cy="2060"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1194955</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>7468</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1942016</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>134471</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="Connector: Elbow 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AF01764-C047-4C64-87E1-5159F5177920}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="1180269" y="8609086"/>
+          <a:ext cx="1440298" cy="747061"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 100259"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>113685</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>72757</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>494685</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>169875</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="20" name="Connector: Elbow 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F57FDFE-A4DC-4F99-928E-AC405C502801}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000" flipH="1" flipV="1">
+          <a:off x="10415626" y="4026566"/>
+          <a:ext cx="1430618" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 264"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>83208</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>39582</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>1281542</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>46182</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="21" name="Straight Arrow Connector 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FD1FC7B-D712-4ABD-A775-A56FA746AC68}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15912026" y="4334491"/>
+          <a:ext cx="1198334" cy="6600"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
           <a:schemeClr val="accent1"/>
         </a:effectRef>
         <a:fontRef idx="minor">
@@ -1625,8 +4052,1128 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD2251F7-615A-45C5-AB51-9631C6BD4189}">
-  <dimension ref="B1:J21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C5B1742-80BA-4BEE-A6A8-C107F8680424}">
+  <dimension ref="N15:O15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="15" spans="14:15" x14ac:dyDescent="0.35">
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24775ADE-03D3-4D0A-807B-37E1A793A03E}">
+  <dimension ref="B3:AE12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="12" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="15.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="B3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S3" t="s">
+        <v>26</v>
+      </c>
+      <c r="T3" t="s">
+        <v>27</v>
+      </c>
+      <c r="U3" t="s">
+        <v>28</v>
+      </c>
+      <c r="V3" t="s">
+        <v>29</v>
+      </c>
+      <c r="W3" t="s">
+        <v>30</v>
+      </c>
+      <c r="X3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="B4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4" t="s">
+        <v>19</v>
+      </c>
+      <c r="P4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>19</v>
+      </c>
+      <c r="R4" t="s">
+        <v>25</v>
+      </c>
+      <c r="S4" t="s">
+        <v>25</v>
+      </c>
+      <c r="T4" t="s">
+        <v>25</v>
+      </c>
+      <c r="U4" t="s">
+        <v>25</v>
+      </c>
+      <c r="V4" t="s">
+        <v>25</v>
+      </c>
+      <c r="W4" t="s">
+        <v>25</v>
+      </c>
+      <c r="X4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="8">
+        <v>84</v>
+      </c>
+      <c r="D5">
+        <v>79.8</v>
+      </c>
+      <c r="E5">
+        <v>57.9</v>
+      </c>
+      <c r="F5">
+        <v>31.2</v>
+      </c>
+      <c r="G5" s="8">
+        <v>65</v>
+      </c>
+      <c r="H5">
+        <v>43.2</v>
+      </c>
+      <c r="I5">
+        <v>8.6</v>
+      </c>
+      <c r="J5">
+        <v>30.2</v>
+      </c>
+      <c r="K5">
+        <v>22.2</v>
+      </c>
+      <c r="L5">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="M5" s="8">
+        <v>90.3</v>
+      </c>
+      <c r="N5">
+        <v>19.7</v>
+      </c>
+      <c r="O5" s="8">
+        <v>84.7</v>
+      </c>
+      <c r="P5" s="8">
+        <v>66.7</v>
+      </c>
+      <c r="Q5">
+        <v>36.1</v>
+      </c>
+      <c r="R5">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="S5">
+        <v>89.7</v>
+      </c>
+      <c r="T5">
+        <v>54.7</v>
+      </c>
+      <c r="U5">
+        <v>28.7</v>
+      </c>
+      <c r="V5">
+        <v>46.3</v>
+      </c>
+      <c r="W5">
+        <v>41.7</v>
+      </c>
+      <c r="X5" s="7">
+        <v>91.7</v>
+      </c>
+      <c r="Y5" s="7">
+        <v>63.8</v>
+      </c>
+      <c r="Z5">
+        <v>4.8</v>
+      </c>
+      <c r="AA5">
+        <v>29.2</v>
+      </c>
+      <c r="AB5">
+        <v>7.1</v>
+      </c>
+      <c r="AC5" s="7">
+        <v>53.5</v>
+      </c>
+      <c r="AD5" s="7">
+        <v>31.9</v>
+      </c>
+      <c r="AE5" s="7">
+        <v>95.9</v>
+      </c>
+    </row>
+    <row r="6" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="B6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4">
+        <v>83.4</v>
+      </c>
+      <c r="D6">
+        <v>83</v>
+      </c>
+      <c r="E6">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="F6">
+        <v>84.4</v>
+      </c>
+      <c r="G6">
+        <v>1.3</v>
+      </c>
+      <c r="H6" s="4">
+        <v>84.7</v>
+      </c>
+      <c r="I6">
+        <v>16.8</v>
+      </c>
+      <c r="J6">
+        <v>24.1</v>
+      </c>
+      <c r="K6">
+        <v>64.900000000000006</v>
+      </c>
+      <c r="L6">
+        <v>84</v>
+      </c>
+      <c r="M6" s="4">
+        <v>46</v>
+      </c>
+      <c r="N6">
+        <v>52.8</v>
+      </c>
+      <c r="O6">
+        <v>40.4</v>
+      </c>
+      <c r="P6" s="4">
+        <v>60.3</v>
+      </c>
+      <c r="Q6">
+        <v>45</v>
+      </c>
+      <c r="R6">
+        <v>72.5</v>
+      </c>
+      <c r="S6" s="4">
+        <v>99</v>
+      </c>
+      <c r="T6">
+        <v>20.9</v>
+      </c>
+      <c r="U6">
+        <v>22.8</v>
+      </c>
+      <c r="V6">
+        <v>4.8</v>
+      </c>
+      <c r="W6">
+        <v>5.9</v>
+      </c>
+      <c r="X6" s="8">
+        <v>71.5</v>
+      </c>
+      <c r="Y6">
+        <v>63.3</v>
+      </c>
+      <c r="Z6">
+        <v>50.4</v>
+      </c>
+      <c r="AA6" s="4">
+        <v>95.8</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>93.3</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>77.599999999999994</v>
+      </c>
+      <c r="AD6">
+        <v>13.3</v>
+      </c>
+      <c r="AE6">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="7" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="B7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>68.8</v>
+      </c>
+      <c r="D7">
+        <v>69.2</v>
+      </c>
+      <c r="E7">
+        <v>19.8</v>
+      </c>
+      <c r="F7" s="3">
+        <v>98.5</v>
+      </c>
+      <c r="G7">
+        <v>39.6</v>
+      </c>
+      <c r="H7">
+        <v>67.900000000000006</v>
+      </c>
+      <c r="I7">
+        <v>44.5</v>
+      </c>
+      <c r="J7">
+        <v>46.3</v>
+      </c>
+      <c r="K7" s="3">
+        <v>96.8</v>
+      </c>
+      <c r="L7">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="M7" s="8">
+        <v>50.9</v>
+      </c>
+      <c r="N7" s="3">
+        <v>76.7</v>
+      </c>
+      <c r="O7">
+        <v>28.3</v>
+      </c>
+      <c r="P7">
+        <v>8.5</v>
+      </c>
+      <c r="Q7">
+        <v>14.3</v>
+      </c>
+      <c r="R7">
+        <v>47.4</v>
+      </c>
+      <c r="S7">
+        <v>58.9</v>
+      </c>
+      <c r="T7">
+        <v>55.1</v>
+      </c>
+      <c r="U7">
+        <v>16.3</v>
+      </c>
+      <c r="V7" s="3">
+        <v>83.9</v>
+      </c>
+      <c r="W7" s="3">
+        <v>70</v>
+      </c>
+      <c r="X7">
+        <v>52.5</v>
+      </c>
+      <c r="Y7">
+        <v>3.4</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>57.9</v>
+      </c>
+      <c r="AA7">
+        <v>93.4</v>
+      </c>
+      <c r="AB7">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="AC7">
+        <v>15.6</v>
+      </c>
+      <c r="AD7">
+        <v>17.2</v>
+      </c>
+      <c r="AE7">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="D8">
+        <v>56.2</v>
+      </c>
+      <c r="E8">
+        <v>12.4</v>
+      </c>
+      <c r="F8">
+        <v>83</v>
+      </c>
+      <c r="G8">
+        <v>26.3</v>
+      </c>
+      <c r="H8">
+        <v>21.3</v>
+      </c>
+      <c r="I8" s="6">
+        <v>76.400000000000006</v>
+      </c>
+      <c r="J8">
+        <v>47.8</v>
+      </c>
+      <c r="K8">
+        <v>78.8</v>
+      </c>
+      <c r="L8" s="6">
+        <v>89.1</v>
+      </c>
+      <c r="M8">
+        <v>7.4</v>
+      </c>
+      <c r="N8">
+        <v>0.7</v>
+      </c>
+      <c r="O8" s="6">
+        <v>43.9</v>
+      </c>
+      <c r="P8">
+        <v>31.8</v>
+      </c>
+      <c r="Q8">
+        <v>51.8</v>
+      </c>
+      <c r="R8" s="8">
+        <v>84.3</v>
+      </c>
+      <c r="S8">
+        <v>57.6</v>
+      </c>
+      <c r="T8">
+        <v>77.8</v>
+      </c>
+      <c r="U8" s="6">
+        <v>96.9</v>
+      </c>
+      <c r="V8">
+        <v>58.1</v>
+      </c>
+      <c r="W8">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="X8">
+        <v>70.3</v>
+      </c>
+      <c r="Y8" s="8">
+        <v>70.5</v>
+      </c>
+      <c r="Z8" s="8">
+        <v>63.4</v>
+      </c>
+      <c r="AA8">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="AB8">
+        <v>63.2</v>
+      </c>
+      <c r="AC8">
+        <v>5.3</v>
+      </c>
+      <c r="AD8">
+        <v>31.2</v>
+      </c>
+      <c r="AE8" s="8">
+        <v>85.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="B9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>19.8</v>
+      </c>
+      <c r="D9" s="5">
+        <v>91</v>
+      </c>
+      <c r="E9" s="5">
+        <v>95.3</v>
+      </c>
+      <c r="F9">
+        <v>7.2</v>
+      </c>
+      <c r="G9" s="5">
+        <v>54.9</v>
+      </c>
+      <c r="H9">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="I9">
+        <v>73.099999999999994</v>
+      </c>
+      <c r="J9" s="5">
+        <v>87.1</v>
+      </c>
+      <c r="K9">
+        <v>7</v>
+      </c>
+      <c r="L9">
+        <v>22.4</v>
+      </c>
+      <c r="M9">
+        <v>7.2</v>
+      </c>
+      <c r="N9">
+        <v>1.3</v>
+      </c>
+      <c r="O9">
+        <v>12.6</v>
+      </c>
+      <c r="P9">
+        <v>27.9</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>73.3</v>
+      </c>
+      <c r="R9" s="5">
+        <v>74.900000000000006</v>
+      </c>
+      <c r="S9">
+        <v>92.4</v>
+      </c>
+      <c r="T9" s="5">
+        <v>86</v>
+      </c>
+      <c r="U9">
+        <v>82</v>
+      </c>
+      <c r="V9">
+        <v>70.2</v>
+      </c>
+      <c r="W9">
+        <v>26.7</v>
+      </c>
+      <c r="X9">
+        <v>7</v>
+      </c>
+      <c r="Y9">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="Z9">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AA9">
+        <v>58.4</v>
+      </c>
+      <c r="AB9" s="5">
+        <v>64.900000000000006</v>
+      </c>
+      <c r="AC9">
+        <v>24.3</v>
+      </c>
+      <c r="AD9" s="8">
+        <v>48.1</v>
+      </c>
+      <c r="AE9">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="10" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="B10" s="1"/>
+      <c r="C10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+    </row>
+    <row r="11" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="B11" s="1"/>
+      <c r="C11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+    </row>
+    <row r="12" spans="2:31" x14ac:dyDescent="0.35">
+      <c r="B12" s="1"/>
+      <c r="C12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="B3:AE12" xr:uid="{24775ADE-03D3-4D0A-807B-37E1A793A03E}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:AE12">
+      <sortCondition descending="1" ref="C3:C12"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83567D3B-F48D-486C-96F8-0F8805A7B8A0}">
+  <dimension ref="B3:AB30"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="4.7265625" customWidth="1"/>
+    <col min="2" max="2" width="29.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.36328125" customWidth="1"/>
+    <col min="7" max="7" width="3.54296875" customWidth="1"/>
+    <col min="8" max="8" width="13.36328125" customWidth="1"/>
+    <col min="9" max="9" width="13.26953125" customWidth="1"/>
+    <col min="10" max="10" width="3.08984375" style="34" customWidth="1"/>
+    <col min="11" max="11" width="4.453125" customWidth="1"/>
+    <col min="12" max="12" width="4.7265625" customWidth="1"/>
+    <col min="13" max="13" width="24.36328125" customWidth="1"/>
+    <col min="15" max="15" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.453125" customWidth="1"/>
+    <col min="18" max="18" width="3.453125" customWidth="1"/>
+    <col min="22" max="22" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="20.36328125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="20.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:19" s="34" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="2:19" s="55" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="J4" s="34"/>
+      <c r="M4" s="37" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="F5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B6" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" t="s">
+        <v>77</v>
+      </c>
+      <c r="M6" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B8" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="M8" s="38" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="38" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B9" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q9" s="39" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B10" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="M10" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q10" s="39" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B11" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="54" t="s">
+        <v>78</v>
+      </c>
+      <c r="H11" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="M11" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q11" s="43" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B12" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="M12" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q12" s="67" t="s">
+        <v>78</v>
+      </c>
+      <c r="S12" s="53" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B13" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="M13" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q13" s="67" t="s">
+        <v>78</v>
+      </c>
+      <c r="S13" s="53" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="41" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M15" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="S15" s="53" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="C17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="C18" t="s">
+        <v>80</v>
+      </c>
+      <c r="N18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="C20" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="N20" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="O20" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="P20" s="46" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="C21" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="49">
+        <v>83.9</v>
+      </c>
+      <c r="N21" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="O21" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="P21" s="49">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="C22" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="49">
+        <v>70</v>
+      </c>
+      <c r="N22" s="47" t="s">
+        <v>34</v>
+      </c>
+      <c r="O22" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="P22" s="49">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="C23" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="49">
+        <v>76.7</v>
+      </c>
+      <c r="N23" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="O23" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="P23" s="49">
+        <v>93.3</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="C24" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="49">
+        <v>98.5</v>
+      </c>
+      <c r="N24" s="61" t="s">
+        <v>36</v>
+      </c>
+      <c r="O24" s="62" t="s">
+        <v>25</v>
+      </c>
+      <c r="P24" s="63">
+        <v>77.599999999999994</v>
+      </c>
+      <c r="T24" t="s">
+        <v>83</v>
+      </c>
+      <c r="W24" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="C25" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="49">
+        <v>96.8</v>
+      </c>
+      <c r="N25" s="47" t="s">
+        <v>13</v>
+      </c>
+      <c r="O25" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="P25" s="49">
+        <v>84.7</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C26" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="52"/>
+      <c r="N26" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="O26" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="P26" s="66"/>
+      <c r="W26" t="s">
+        <v>81</v>
+      </c>
+      <c r="X26" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="N27" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="O27" s="65" t="s">
+        <v>19</v>
+      </c>
+      <c r="P27" s="66"/>
+      <c r="W27" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X27" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z27" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA27" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB27" s="46" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="N28" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="O28" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="P28" s="52"/>
+      <c r="W28" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="X28" s="57" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y28" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z28" s="57">
+        <v>77.599999999999994</v>
+      </c>
+      <c r="AA28" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB28" s="60">
+        <v>53.5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" s="34" customFormat="1" x14ac:dyDescent="0.35"/>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="W28:Z28" location="'Stage 2'!A1" display="VP7" xr:uid="{CBCD99EA-834C-4796-83E9-942C35EA0FC7}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3C59DEC-47E9-43C1-92E4-29A66567C895}">
+  <dimension ref="B1:G21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
@@ -1634,12 +5181,12 @@
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:7" x14ac:dyDescent="0.35">
       <c r="D1" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
       <c r="D3" s="15" t="s">
         <v>39</v>
       </c>
@@ -1653,7 +5200,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
         <v>42</v>
       </c>
@@ -1670,7 +5217,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
         <v>43</v>
       </c>
@@ -1687,7 +5234,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
         <v>44</v>
       </c>
@@ -1704,7 +5251,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C7" t="s">
         <v>45</v>
       </c>
@@ -1721,7 +5268,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
         <v>46</v>
       </c>
@@ -1738,7 +5285,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C9" s="21" t="s">
         <v>47</v>
       </c>
@@ -1756,13 +5303,13 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="2:10" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:7" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C13" s="19" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>49</v>
       </c>
@@ -1771,10 +5318,8 @@
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="22" t="s">
         <v>50</v>
       </c>
@@ -1817,11 +5362,10 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EFAC392-3DBC-4888-8676-CE4E321B2BF1}">
   <dimension ref="B1:Q30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2670,7 +6214,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91DB8E5F-AF7D-41D4-BF57-6A1EA4CEA7A3}">
   <dimension ref="B2:Q31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2686,7 +6230,7 @@
     <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
@@ -2721,26 +6265,26 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B3" t="s">
+    <row r="3" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="26">
         <v>68.8</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="30">
         <v>83.4</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="26">
         <v>19.8</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="26">
         <v>38.200000000000003</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="33">
         <v>84</v>
       </c>
       <c r="K3" t="s">
@@ -2835,7 +6379,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
         <v>11</v>
       </c>
@@ -2873,26 +6417,26 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B7" t="s">
+    <row r="7" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="26">
         <v>39.6</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="26">
         <v>1.3</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="30">
         <v>54.9</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="26">
         <v>26.3</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="33">
         <v>65</v>
       </c>
       <c r="K7" t="s">
@@ -3017,35 +6561,35 @@
       <c r="K11" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="23" t="s">
+      <c r="L11" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
     </row>
     <row r="12" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+      <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12">
         <v>78.900000000000006</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12">
         <v>84</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12">
         <v>22.4</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="4">
         <v>89.1</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12">
         <v>35.700000000000003</v>
       </c>
       <c r="K12" s="13" t="s">
@@ -3060,26 +6604,26 @@
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B13" t="s">
+    <row r="13" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B13" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="30">
         <v>50.9</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="26">
         <v>46</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="26">
         <v>7.2</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="26">
         <v>7.4</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="33">
         <v>90.3</v>
       </c>
       <c r="K13" s="4"/>
@@ -3092,7 +6636,7 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B14" t="s">
         <v>20</v>
       </c>
@@ -3124,26 +6668,26 @@
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B15" t="s">
+    <row r="15" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B15" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="26">
         <v>28.3</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="26">
         <v>40.4</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="26">
         <v>12.6</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="30">
         <v>43.9</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="33">
         <v>84.7</v>
       </c>
       <c r="K15" s="4"/>
@@ -3156,26 +6700,26 @@
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B16" t="s">
+    <row r="16" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="26">
         <v>8.5</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="30">
         <v>60.3</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="26">
         <v>27.9</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="26">
         <v>31.8</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="33">
         <v>66.7</v>
       </c>
       <c r="K16" t="s">
@@ -3214,26 +6758,26 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B18" t="s">
+    <row r="18" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="C18" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18">
+      <c r="C18" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="26">
         <v>47.4</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="26">
         <v>72.5</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="30">
         <v>74.900000000000006</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="27">
         <v>84.3</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="31">
         <v>18.899999999999999</v>
       </c>
     </row>
@@ -3352,7 +6896,7 @@
         <v>41.7</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B24" t="s">
         <v>31</v>
       </c>
@@ -3375,49 +6919,49 @@
         <v>91.7</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B25" t="s">
+    <row r="25" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25">
+      <c r="C25" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="26">
         <v>3.4</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="26">
         <v>63.3</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="26">
         <v>36.200000000000003</v>
       </c>
-      <c r="G25" s="14">
+      <c r="G25" s="27">
         <v>70.5</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="28">
         <v>63.8</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B26" t="s">
+    <row r="26" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C26" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" s="13">
+      <c r="C26" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="30">
         <v>57.9</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="26">
         <v>50.4</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="26">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G26" s="14">
+      <c r="G26" s="27">
         <v>63.4</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="31">
         <v>4.8</v>
       </c>
     </row>
@@ -3444,7 +6988,7 @@
         <v>29.2</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B28" t="s">
         <v>35</v>
       </c>
@@ -3467,30 +7011,30 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B29" t="s">
+    <row r="29" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="C29" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29">
+      <c r="C29" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="26">
         <v>15.6</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E29" s="27">
         <v>77.599999999999994</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="26">
         <v>24.3</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="26">
         <v>5.3</v>
       </c>
-      <c r="H29" s="13">
+      <c r="H29" s="28">
         <v>53.5</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B30" t="s">
         <v>37</v>
       </c>
@@ -3513,26 +7057,26 @@
         <v>31.9</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B31" t="s">
+    <row r="31" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B31" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="C31" t="s">
-        <v>25</v>
-      </c>
-      <c r="D31">
+      <c r="C31" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="26">
         <v>5.0999999999999996</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="26">
         <v>9.9</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="26">
         <v>60.4</v>
       </c>
-      <c r="G31" s="14">
+      <c r="G31" s="27">
         <v>85.5</v>
       </c>
-      <c r="H31" s="13">
+      <c r="H31" s="28">
         <v>95.9</v>
       </c>
     </row>
@@ -3545,7 +7089,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C152A9E-0EE5-44A0-960E-9E1CD6B00E9D}">
   <dimension ref="B2:R31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3892,14 +7436,14 @@
       <c r="K11" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="23" t="s">
+      <c r="L11" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
     </row>
     <row r="12" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" s="9" t="s">
@@ -4407,7 +7951,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86D0E5D6-7A76-4E6F-A0DD-59D4DB683A8B}">
   <dimension ref="B2:T31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4875,14 +8419,14 @@
       <c r="E25" t="s">
         <v>49</v>
       </c>
-      <c r="F25" s="23" t="s">
+      <c r="F25" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="36"/>
+      <c r="J25" s="36"/>
+      <c r="K25" s="36"/>
     </row>
     <row r="26" spans="5:13" x14ac:dyDescent="0.35">
       <c r="E26" t="s">
@@ -4941,9 +8485,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA088233-5EF0-45F9-8BF7-5534FE391935}">
-  <dimension ref="B2:T73"/>
+  <dimension ref="A3:T126"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.6328125" customWidth="1"/>
@@ -4951,10 +8495,11 @@
     <col min="3" max="3" width="15.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.36328125" customWidth="1"/>
-    <col min="6" max="6" width="14.453125" customWidth="1"/>
+    <col min="6" max="6" width="20.7265625" customWidth="1"/>
     <col min="7" max="7" width="17.1796875" customWidth="1"/>
-    <col min="8" max="8" width="13.90625" customWidth="1"/>
+    <col min="8" max="8" width="22.36328125" customWidth="1"/>
     <col min="9" max="9" width="4.6328125" customWidth="1"/>
+    <col min="10" max="10" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.26953125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="4.453125" customWidth="1"/>
@@ -4967,1966 +8512,1846 @@
     <col min="20" max="20" width="10.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B2" s="30" t="s">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C3" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B4" s="10" t="s">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="34"/>
+      <c r="P5" s="34"/>
+      <c r="Q5" s="34"/>
+      <c r="R5" s="34"/>
+      <c r="S5" s="34"/>
+      <c r="T5" s="34"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B8" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C8" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D8" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F8" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G8" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H8" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J8" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K8" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L8" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="10" t="s">
+      <c r="N8" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="O8" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="P4" s="10" t="s">
+      <c r="P8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="R4" s="10" t="s">
+      <c r="R8" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="S4" s="10" t="s">
+      <c r="S8" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="T4" s="10" t="s">
+      <c r="T8" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B5" t="s">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
         <v>29</v>
       </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="26">
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="4">
         <v>83.9</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F9" t="s">
         <v>26</v>
       </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="26">
+      <c r="G9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="4">
         <v>99</v>
       </c>
-      <c r="I5" s="1"/>
-      <c r="J5" t="s">
+      <c r="I9" s="1"/>
+      <c r="J9" t="s">
         <v>27</v>
       </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="26">
+      <c r="K9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="4">
         <v>86</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N9" t="s">
         <v>28</v>
       </c>
-      <c r="O5" t="s">
-        <v>25</v>
-      </c>
-      <c r="P5" s="26">
+      <c r="O9" t="s">
+        <v>25</v>
+      </c>
+      <c r="P9" s="4">
         <v>96.9</v>
       </c>
-      <c r="R5" t="s">
+      <c r="R9" t="s">
         <v>31</v>
       </c>
-      <c r="S5" t="s">
-        <v>25</v>
-      </c>
-      <c r="T5" s="26">
+      <c r="S9" t="s">
+        <v>25</v>
+      </c>
+      <c r="T9" s="4">
         <v>91.7</v>
       </c>
     </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B6" t="s">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
         <v>30</v>
       </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="26">
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="4">
         <v>70</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F10" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="28">
+      <c r="G10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="4">
         <v>95.8</v>
       </c>
-      <c r="I6" s="1"/>
-      <c r="J6" t="s">
+      <c r="I10" s="1"/>
+      <c r="J10" t="s">
         <v>37</v>
       </c>
-      <c r="K6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" s="26">
+      <c r="K10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="4">
         <v>48.1</v>
       </c>
-      <c r="N6" s="24" t="s">
+      <c r="N10" t="s">
         <v>38</v>
       </c>
-      <c r="O6" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="P6" s="26">
+      <c r="O10" t="s">
+        <v>25</v>
+      </c>
+      <c r="P10" s="4">
         <v>85.5</v>
       </c>
-      <c r="R6" s="24" t="s">
+      <c r="R10" t="s">
         <v>18</v>
       </c>
-      <c r="S6" s="24" t="s">
+      <c r="S10" t="s">
         <v>19</v>
       </c>
-      <c r="T6" s="26">
+      <c r="T10" s="4">
         <v>90.3</v>
       </c>
     </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B7" t="s">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
         <v>20</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C11" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D11" s="4">
         <v>76.7</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F11" t="s">
         <v>35</v>
       </c>
-      <c r="G7" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="26">
+      <c r="G11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="4">
         <v>93.3</v>
       </c>
-      <c r="I7" s="1"/>
-      <c r="J7" t="s">
+      <c r="I11" s="1"/>
+      <c r="J11" t="s">
         <v>23</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K11" t="s">
         <v>19</v>
       </c>
-      <c r="L7" s="26">
+      <c r="L11" s="4">
         <v>73.3</v>
       </c>
-      <c r="N7" s="24" t="s">
+      <c r="N11" t="s">
         <v>24</v>
       </c>
-      <c r="O7" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="P7" s="26">
+      <c r="O11" t="s">
+        <v>25</v>
+      </c>
+      <c r="P11" s="4">
         <v>84.3</v>
       </c>
-      <c r="R7" s="33" t="s">
+      <c r="R11" t="s">
         <v>21</v>
       </c>
-      <c r="S7" s="33" t="s">
+      <c r="S11" t="s">
         <v>19</v>
       </c>
-      <c r="T7" s="28">
+      <c r="T11" s="4">
         <v>84.7</v>
       </c>
     </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B8" t="s">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
         <v>11</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C12" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D12" s="4">
         <v>98.5</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F12" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="26">
+      <c r="G12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="4">
         <v>77.599999999999994</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J12" t="s">
         <v>10</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K12" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="26">
+      <c r="L12" s="4">
         <v>95.3</v>
       </c>
-      <c r="N8" s="24" t="s">
+      <c r="N12" t="s">
         <v>32</v>
       </c>
-      <c r="O8" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="P8" s="26">
+      <c r="O12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P12" s="4">
         <v>70.5</v>
       </c>
-      <c r="R8" s="33" t="s">
+      <c r="R12" t="s">
         <v>22</v>
       </c>
-      <c r="S8" s="33" t="s">
+      <c r="S12" t="s">
         <v>19</v>
       </c>
-      <c r="T8" s="28">
+      <c r="T12" s="4">
         <v>66.7</v>
       </c>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B9" t="s">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
         <v>16</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C13" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D13" s="4">
         <v>96.8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F13" t="s">
         <v>13</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G13" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="26">
+      <c r="H13" s="4">
         <v>84.7</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J13" t="s">
         <v>9</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K13" t="s">
         <v>8</v>
       </c>
-      <c r="L9" s="26">
+      <c r="L13" s="4">
         <v>91</v>
       </c>
-      <c r="N9" s="24" t="s">
+      <c r="N13" t="s">
         <v>33</v>
       </c>
-      <c r="O9" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="P9" s="26">
+      <c r="O13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P13" s="4">
         <v>63.4</v>
       </c>
-      <c r="R9" s="24" t="s">
+      <c r="R13" t="s">
         <v>7</v>
       </c>
-      <c r="S9" s="24" t="s">
+      <c r="S13" t="s">
         <v>8</v>
       </c>
-      <c r="T9" s="26">
+      <c r="T13" s="4">
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="J10" t="s">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="J14" t="s">
         <v>15</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K14" t="s">
         <v>8</v>
       </c>
-      <c r="L10" s="26">
+      <c r="L14" s="4">
         <v>87.1</v>
       </c>
-      <c r="N10" t="s">
+      <c r="N14" t="s">
         <v>17</v>
       </c>
-      <c r="O10" t="s">
+      <c r="O14" t="s">
         <v>8</v>
       </c>
-      <c r="P10" s="26">
+      <c r="P14" s="4">
         <v>89.1</v>
       </c>
-      <c r="R10" s="24" t="s">
+      <c r="R14" t="s">
         <v>12</v>
       </c>
-      <c r="S10" s="24" t="s">
+      <c r="S14" t="s">
         <v>8</v>
       </c>
-      <c r="T10" s="26">
+      <c r="T14" s="4">
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="N11" t="s">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="N15" t="s">
         <v>14</v>
       </c>
-      <c r="O11" t="s">
+      <c r="O15" t="s">
         <v>8</v>
       </c>
-      <c r="P11" s="26">
+      <c r="P15" s="4">
         <v>76.400000000000006</v>
       </c>
-      <c r="R11" s="24"/>
-      <c r="S11" s="24"/>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="P12" s="29"/>
-      <c r="R12" s="24"/>
-      <c r="S12" s="24"/>
-    </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B13" t="s">
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A16" s="34"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="34"/>
+      <c r="P16" s="34"/>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="34"/>
+      <c r="S16" s="34"/>
+      <c r="T16" s="34"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B18" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="K18" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L18" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="O18" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="P18" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="S18" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="T18" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19">
+        <v>83.9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19">
+        <v>99</v>
+      </c>
+      <c r="I19" s="1"/>
+      <c r="J19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K19" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19">
+        <v>86</v>
+      </c>
+      <c r="N19" t="s">
+        <v>28</v>
+      </c>
+      <c r="O19" t="s">
+        <v>25</v>
+      </c>
+      <c r="P19">
+        <v>96.9</v>
+      </c>
+      <c r="R19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S19" t="s">
+        <v>25</v>
+      </c>
+      <c r="T19">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20">
+        <v>70</v>
+      </c>
+      <c r="F20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20">
+        <v>95.8</v>
+      </c>
+      <c r="I20" s="1"/>
+      <c r="J20" t="s">
+        <v>37</v>
+      </c>
+      <c r="K20" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20">
+        <v>48.1</v>
+      </c>
+      <c r="N20" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="O20" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="P20" s="29">
+        <v>85.5</v>
+      </c>
+      <c r="R20" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="S20" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="T20" s="29">
+        <v>90.3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21">
+        <v>76.7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21">
+        <v>93.3</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" t="s">
+        <v>23</v>
+      </c>
+      <c r="K21" t="s">
+        <v>19</v>
+      </c>
+      <c r="L21">
+        <v>73.3</v>
+      </c>
+      <c r="N21" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="O21" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="P21" s="29">
+        <v>84.3</v>
+      </c>
+      <c r="R21" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="S21" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="T21" s="29">
+        <v>84.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22">
+        <v>98.5</v>
+      </c>
+      <c r="F22" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" s="29">
+        <v>77.599999999999994</v>
+      </c>
+      <c r="J22" t="s">
+        <v>10</v>
+      </c>
+      <c r="K22" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22">
+        <v>95.3</v>
+      </c>
+      <c r="N22" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="O22" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="P22" s="29">
+        <v>70.5</v>
+      </c>
+      <c r="R22" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="S22" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="T22" s="29">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23">
+        <v>96.8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23">
+        <v>84.7</v>
+      </c>
+      <c r="J23" t="s">
+        <v>9</v>
+      </c>
+      <c r="K23" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23">
+        <v>91</v>
+      </c>
+      <c r="N23" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="O23" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="P23" s="29">
+        <v>63.4</v>
+      </c>
+      <c r="R23" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="S23" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="T23" s="29">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B24" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="23"/>
+      <c r="F24" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="G24" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="H24" s="23"/>
+      <c r="J24" t="s">
+        <v>15</v>
+      </c>
+      <c r="K24" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24">
+        <v>87.1</v>
+      </c>
+      <c r="N24" t="s">
+        <v>17</v>
+      </c>
+      <c r="O24" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24">
+        <v>89.1</v>
+      </c>
+      <c r="R24" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="S24" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="T24" s="29">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="F25" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" s="23"/>
+      <c r="J25" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="K25" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="L25" s="23"/>
+      <c r="N25" t="s">
+        <v>14</v>
+      </c>
+      <c r="O25" t="s">
+        <v>8</v>
+      </c>
+      <c r="P25">
+        <v>76.400000000000006</v>
+      </c>
+      <c r="R25" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="S25" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="T25" s="23"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="F26" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="G26" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" s="23"/>
+      <c r="J26" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="K26" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="23"/>
+      <c r="N26" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="O26" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="P26" s="23"/>
+      <c r="R26" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="S26" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="T26" s="23"/>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="R27" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="S27" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="T27" s="23"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="R28" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="S28" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="T28" s="23"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="R29" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="S29" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="T29" s="23"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A30" s="34"/>
+      <c r="B30" s="34"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="34"/>
+      <c r="K30" s="34"/>
+      <c r="L30" s="34"/>
+      <c r="M30" s="34"/>
+      <c r="N30" s="34"/>
+      <c r="O30" s="34"/>
+      <c r="P30" s="34"/>
+      <c r="Q30" s="34"/>
+      <c r="R30" s="34"/>
+      <c r="S30" s="34"/>
+      <c r="T30" s="34"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B31" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B32" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L32" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="O32" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="P32" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="S32" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="T32" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33">
+        <v>83.9</v>
+      </c>
+      <c r="F33" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" t="s">
+        <v>25</v>
+      </c>
+      <c r="H33">
+        <v>99</v>
+      </c>
+      <c r="I33" s="1"/>
+      <c r="J33" t="s">
+        <v>27</v>
+      </c>
+      <c r="K33" t="s">
+        <v>25</v>
+      </c>
+      <c r="L33">
+        <v>86</v>
+      </c>
+      <c r="N33" t="s">
+        <v>28</v>
+      </c>
+      <c r="O33" t="s">
+        <v>25</v>
+      </c>
+      <c r="P33">
+        <v>96.9</v>
+      </c>
+      <c r="R33" t="s">
+        <v>31</v>
+      </c>
+      <c r="S33" t="s">
+        <v>25</v>
+      </c>
+      <c r="T33">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34">
+        <v>70</v>
+      </c>
+      <c r="F34" t="s">
+        <v>34</v>
+      </c>
+      <c r="G34" t="s">
+        <v>25</v>
+      </c>
+      <c r="H34">
+        <v>95.8</v>
+      </c>
+      <c r="I34" s="1"/>
+      <c r="J34" t="s">
+        <v>37</v>
+      </c>
+      <c r="K34" t="s">
+        <v>25</v>
+      </c>
+      <c r="L34">
+        <v>48.1</v>
+      </c>
+      <c r="N34" s="29"/>
+      <c r="O34" s="29"/>
+      <c r="P34" s="29"/>
+      <c r="R34" s="29"/>
+      <c r="S34" s="29"/>
+      <c r="T34" s="29"/>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35">
+        <v>76.7</v>
+      </c>
+      <c r="F35" t="s">
+        <v>35</v>
+      </c>
+      <c r="G35" t="s">
+        <v>25</v>
+      </c>
+      <c r="H35">
+        <v>93.3</v>
+      </c>
+      <c r="I35" s="1"/>
+      <c r="J35" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" t="s">
+        <v>19</v>
+      </c>
+      <c r="L35">
+        <v>73.3</v>
+      </c>
+      <c r="N35" s="29"/>
+      <c r="O35" s="29"/>
+      <c r="P35" s="29"/>
+      <c r="R35" s="29"/>
+      <c r="S35" s="29"/>
+      <c r="T35" s="29"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B36" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36">
+        <v>98.5</v>
+      </c>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="J36" t="s">
+        <v>10</v>
+      </c>
+      <c r="K36" t="s">
+        <v>8</v>
+      </c>
+      <c r="L36">
+        <v>95.3</v>
+      </c>
+      <c r="N36" s="29"/>
+      <c r="O36" s="29"/>
+      <c r="P36" s="29"/>
+      <c r="R36" s="29"/>
+      <c r="S36" s="29"/>
+      <c r="T36" s="29"/>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37">
+        <v>96.8</v>
+      </c>
+      <c r="F37" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" t="s">
+        <v>8</v>
+      </c>
+      <c r="H37">
+        <v>84.7</v>
+      </c>
+      <c r="J37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K37" t="s">
+        <v>8</v>
+      </c>
+      <c r="L37">
+        <v>91</v>
+      </c>
+      <c r="N37" s="29"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="29"/>
+      <c r="R37" s="29"/>
+      <c r="S37" s="29"/>
+      <c r="T37" s="29"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B38" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D38" s="23"/>
+      <c r="F38" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="G38" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="H38" s="23"/>
+      <c r="J38" t="s">
+        <v>15</v>
+      </c>
+      <c r="K38" t="s">
+        <v>8</v>
+      </c>
+      <c r="L38">
+        <v>87.1</v>
+      </c>
+      <c r="N38" t="s">
+        <v>17</v>
+      </c>
+      <c r="O38" t="s">
+        <v>8</v>
+      </c>
+      <c r="P38">
+        <v>89.1</v>
+      </c>
+      <c r="R38" s="29"/>
+      <c r="S38" s="29"/>
+      <c r="T38" s="29"/>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="F39" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="G39" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" s="23"/>
+      <c r="J39" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="K39" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="L39" s="23"/>
+      <c r="N39" t="s">
+        <v>14</v>
+      </c>
+      <c r="O39" t="s">
+        <v>8</v>
+      </c>
+      <c r="P39">
+        <v>76.400000000000006</v>
+      </c>
+      <c r="R39" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="S39" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="T39" s="23"/>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="F40" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="G40" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" s="23"/>
+      <c r="J40" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="K40" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="L40" s="23"/>
+      <c r="N40" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="O40" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="P40" s="23"/>
+      <c r="R40" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="S40" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="T40" s="23"/>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="R41" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="S41" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="T41" s="23"/>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="R42" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="S42" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="T42" s="23"/>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="R43" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="S43" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="T43" s="23"/>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A44" s="34"/>
+      <c r="B44" s="34"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="34"/>
+      <c r="G44" s="34"/>
+      <c r="H44" s="34"/>
+      <c r="I44" s="34"/>
+      <c r="J44" s="34"/>
+      <c r="K44" s="34"/>
+      <c r="L44" s="34"/>
+      <c r="M44" s="34"/>
+      <c r="N44" s="34"/>
+      <c r="O44" s="34"/>
+      <c r="P44" s="34"/>
+      <c r="Q44" s="34"/>
+      <c r="R44" s="34"/>
+      <c r="S44" s="34"/>
+      <c r="T44" s="34"/>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B45" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B46" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B47" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C47" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D47" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="29">
+        <v>77.599999999999994</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B48" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C48" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D48" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="29">
+        <v>85.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B49" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" t="s">
+        <v>5</v>
+      </c>
+      <c r="E49" s="29">
+        <v>84.3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B50" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D50" t="s">
+        <v>5</v>
+      </c>
+      <c r="E50" s="29">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B51" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C51" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D51" t="s">
+        <v>5</v>
+      </c>
+      <c r="E51" s="29">
+        <v>63.4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B52" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" t="s">
+        <v>6</v>
+      </c>
+      <c r="E52" s="29">
+        <v>90.3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B53" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" t="s">
+        <v>6</v>
+      </c>
+      <c r="E53" s="29">
+        <v>84.7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B54" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C54" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" t="s">
+        <v>6</v>
+      </c>
+      <c r="E54" s="29">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B55" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" t="s">
+        <v>6</v>
+      </c>
+      <c r="E55" s="29">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B56" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" t="s">
+        <v>6</v>
+      </c>
+      <c r="E56" s="29">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A57" s="34"/>
+      <c r="B57" s="34"/>
+      <c r="C57" s="34"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="34"/>
+      <c r="F57" s="34"/>
+      <c r="G57" s="34"/>
+      <c r="H57" s="34"/>
+      <c r="I57" s="34"/>
+      <c r="J57" s="34"/>
+      <c r="K57" s="34"/>
+      <c r="L57" s="34"/>
+      <c r="M57" s="34"/>
+      <c r="N57" s="34"/>
+      <c r="O57" s="34"/>
+      <c r="P57" s="34"/>
+      <c r="Q57" s="34"/>
+      <c r="R57" s="34"/>
+      <c r="S57" s="34"/>
+      <c r="T57" s="34"/>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B59" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I59" s="10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B60" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C60" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D60" t="s">
+        <v>3</v>
+      </c>
+      <c r="E60" s="24">
+        <v>77.599999999999994</v>
+      </c>
+      <c r="F60" t="s">
+        <v>6</v>
+      </c>
+      <c r="G60" s="35">
+        <v>53.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B61" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C61" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D61" t="s">
+        <v>5</v>
+      </c>
+      <c r="E61" s="24">
+        <v>85.5</v>
+      </c>
+      <c r="F61" t="s">
+        <v>6</v>
+      </c>
+      <c r="G61" s="35">
+        <v>95.9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B62" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D62" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="24">
+        <v>84.3</v>
+      </c>
+      <c r="F62" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="35">
+        <v>74.900000000000006</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B63" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C63" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D63" t="s">
+        <v>5</v>
+      </c>
+      <c r="E63" s="24">
+        <v>70.5</v>
+      </c>
+      <c r="F63" t="s">
+        <v>5</v>
+      </c>
+      <c r="G63" s="35">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B64" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C64" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D64" t="s">
+        <v>5</v>
+      </c>
+      <c r="E64" s="24">
+        <v>63.4</v>
+      </c>
+      <c r="F64" t="s">
+        <v>2</v>
+      </c>
+      <c r="G64" s="35">
+        <v>57.9</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B65" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D65" t="s">
+        <v>6</v>
+      </c>
+      <c r="E65" s="24">
+        <v>90.3</v>
+      </c>
+      <c r="F65" t="s">
+        <v>2</v>
+      </c>
+      <c r="G65">
+        <v>50.9</v>
+      </c>
+      <c r="H65" t="s">
+        <v>3</v>
+      </c>
+      <c r="I65" s="35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B66" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C66" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D66" t="s">
+        <v>6</v>
+      </c>
+      <c r="E66" s="24">
+        <v>84.7</v>
+      </c>
+      <c r="F66" t="s">
+        <v>6</v>
+      </c>
+      <c r="G66" s="35">
+        <v>43.9</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B67" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C67" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" t="s">
+        <v>6</v>
+      </c>
+      <c r="E67" s="24">
+        <v>66.7</v>
+      </c>
+      <c r="F67" t="s">
+        <v>3</v>
+      </c>
+      <c r="G67" s="35">
+        <v>60.3</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B68" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" t="s">
+        <v>6</v>
+      </c>
+      <c r="E68" s="24">
+        <v>84</v>
+      </c>
+      <c r="F68" t="s">
+        <v>3</v>
+      </c>
+      <c r="G68" s="35">
+        <v>83.4</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B69" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C69" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" t="s">
+        <v>6</v>
+      </c>
+      <c r="E69" s="24">
+        <v>65</v>
+      </c>
+      <c r="F69" t="s">
+        <v>4</v>
+      </c>
+      <c r="G69" s="35">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="103" spans="6:10" x14ac:dyDescent="0.35">
+      <c r="G103" t="s">
+        <v>39</v>
+      </c>
+      <c r="H103" t="s">
+        <v>41</v>
+      </c>
+      <c r="I103" t="s">
+        <v>40</v>
+      </c>
+      <c r="J103" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="104" spans="6:10" x14ac:dyDescent="0.35">
+      <c r="F104" t="s">
+        <v>42</v>
+      </c>
+      <c r="G104">
+        <v>2</v>
+      </c>
+      <c r="H104">
+        <v>1</v>
+      </c>
+      <c r="I104" s="23">
+        <v>3</v>
+      </c>
+      <c r="J104" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="6:10" x14ac:dyDescent="0.35">
+      <c r="F105" t="s">
+        <v>43</v>
+      </c>
+      <c r="G105">
+        <v>2</v>
+      </c>
+      <c r="H105" s="23">
+        <v>2</v>
+      </c>
+      <c r="I105" s="23">
+        <v>2</v>
+      </c>
+      <c r="J105" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="6:10" x14ac:dyDescent="0.35">
+      <c r="F106" t="s">
+        <v>44</v>
+      </c>
+      <c r="G106" s="23">
+        <v>4</v>
+      </c>
+      <c r="H106">
+        <v>1</v>
+      </c>
+      <c r="I106" s="23">
+        <v>3</v>
+      </c>
+      <c r="J106" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="6:10" x14ac:dyDescent="0.35">
+      <c r="F107" t="s">
+        <v>45</v>
+      </c>
+      <c r="G107">
+        <v>2</v>
+      </c>
+      <c r="H107">
+        <v>1</v>
+      </c>
+      <c r="I107">
+        <v>1</v>
+      </c>
+      <c r="J107" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="6:10" x14ac:dyDescent="0.35">
+      <c r="F108" t="s">
+        <v>46</v>
+      </c>
+      <c r="G108">
+        <v>0</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108">
+        <v>5</v>
+      </c>
+      <c r="J108" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="6:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F109" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G109" s="11">
+        <v>10</v>
+      </c>
+      <c r="H109" s="11">
+        <v>5</v>
+      </c>
+      <c r="I109" s="11">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="110" spans="6:10" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
+    <row r="120" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E120" t="s">
+        <v>49</v>
+      </c>
+      <c r="F120" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="G120" s="36"/>
+      <c r="H120" s="36"/>
+      <c r="I120" s="36"/>
+      <c r="J120" s="36"/>
+      <c r="K120" s="36"/>
+    </row>
+    <row r="121" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E121" t="s">
         <v>50</v>
       </c>
-      <c r="C13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B15" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="10" t="s">
+      <c r="F121" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="122" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="F122" t="s">
+        <v>52</v>
+      </c>
+      <c r="M122">
         <v>2</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="K15" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="O15" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="P15" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="R15" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="S15" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="T15" s="10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="29">
-        <v>83.9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="29">
-        <v>99</v>
-      </c>
-      <c r="I16" s="1"/>
-      <c r="J16" t="s">
-        <v>27</v>
-      </c>
-      <c r="K16" t="s">
-        <v>25</v>
-      </c>
-      <c r="L16" s="29">
-        <v>86</v>
-      </c>
-      <c r="M16" s="30"/>
-      <c r="N16" t="s">
-        <v>28</v>
-      </c>
-      <c r="O16" t="s">
-        <v>25</v>
-      </c>
-      <c r="P16" s="29">
-        <v>96.9</v>
-      </c>
-      <c r="R16" t="s">
-        <v>31</v>
-      </c>
-      <c r="S16" t="s">
-        <v>25</v>
-      </c>
-      <c r="T16" s="29">
-        <v>91.7</v>
-      </c>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="29">
-        <v>70</v>
-      </c>
-      <c r="F17" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" s="32">
-        <v>95.8</v>
-      </c>
-      <c r="I17" s="1"/>
-      <c r="J17" t="s">
-        <v>37</v>
-      </c>
-      <c r="K17" t="s">
-        <v>25</v>
-      </c>
-      <c r="L17" s="29">
-        <v>48.1</v>
-      </c>
-      <c r="M17" s="30"/>
-      <c r="N17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="P17" s="31">
-        <v>85.5</v>
-      </c>
-      <c r="R17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="S17" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="T17" s="31">
-        <v>90.3</v>
-      </c>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="29">
-        <v>76.7</v>
-      </c>
-      <c r="F18" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G18" t="s">
-        <v>25</v>
-      </c>
-      <c r="H18" s="29">
-        <v>93.3</v>
-      </c>
-      <c r="I18" s="1"/>
-      <c r="J18" t="s">
-        <v>23</v>
-      </c>
-      <c r="K18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L18" s="29">
-        <v>73.3</v>
-      </c>
-      <c r="M18" s="30"/>
-      <c r="N18" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="O18" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="P18" s="31">
-        <v>84.3</v>
-      </c>
-      <c r="R18" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="S18" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="T18" s="35">
-        <v>84.7</v>
-      </c>
-    </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="29">
-        <v>98.5</v>
-      </c>
-      <c r="F19" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H19" s="31">
-        <v>77.599999999999994</v>
-      </c>
-      <c r="J19" t="s">
-        <v>10</v>
-      </c>
-      <c r="K19" t="s">
-        <v>8</v>
-      </c>
-      <c r="L19" s="29">
-        <v>95.3</v>
-      </c>
-      <c r="M19" s="30"/>
-      <c r="N19" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="O19" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="P19" s="31">
-        <v>70.5</v>
-      </c>
-      <c r="R19" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="S19" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="T19" s="35">
-        <v>66.7</v>
-      </c>
-    </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="29">
-        <v>96.8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" t="s">
-        <v>8</v>
-      </c>
-      <c r="H20" s="29">
-        <v>84.7</v>
-      </c>
-      <c r="J20" t="s">
-        <v>9</v>
-      </c>
-      <c r="K20" t="s">
-        <v>8</v>
-      </c>
-      <c r="L20" s="29">
-        <v>91</v>
-      </c>
-      <c r="M20" s="30"/>
-      <c r="N20" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="O20" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="P20" s="31">
-        <v>63.4</v>
-      </c>
-      <c r="R20" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="S20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="T20" s="31">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B21" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" s="24"/>
-      <c r="F21" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G21" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="H21" s="24"/>
-      <c r="J21" t="s">
-        <v>15</v>
-      </c>
-      <c r="K21" t="s">
-        <v>8</v>
-      </c>
-      <c r="L21" s="29">
-        <v>87.1</v>
-      </c>
-      <c r="N21" t="s">
-        <v>17</v>
-      </c>
-      <c r="O21" t="s">
-        <v>8</v>
-      </c>
-      <c r="P21" s="29">
-        <v>89.1</v>
-      </c>
-      <c r="R21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="S21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="T21" s="31">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="F22" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G22" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="J22" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="K22" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="L22" s="24"/>
-      <c r="N22" t="s">
-        <v>14</v>
-      </c>
-      <c r="O22" t="s">
-        <v>8</v>
-      </c>
-      <c r="P22" s="29">
-        <v>76.400000000000006</v>
-      </c>
-      <c r="R22" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="S22" s="25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="F23" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G23" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="J23" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="K23" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="L23" s="24"/>
-      <c r="N23" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="O23" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="P23" s="24"/>
-      <c r="R23" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="S23" s="25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="P24" s="24"/>
-      <c r="R24" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="S24" s="25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="R25" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="S25" s="25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="J26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
-      <c r="P26" s="24"/>
-      <c r="R26" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="S26" s="25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B27" s="1"/>
-      <c r="F27" s="37"/>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
-      <c r="P27" s="24"/>
-    </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="P28" s="24"/>
-    </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="P29" s="24"/>
-    </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B30" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H30" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="J30" s="24"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
-      <c r="P30" s="24"/>
-    </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B31" t="s">
-        <v>36</v>
-      </c>
-      <c r="C31" t="s">
-        <v>25</v>
-      </c>
-      <c r="D31">
-        <v>15.6</v>
-      </c>
-      <c r="E31" s="4">
-        <v>77.599999999999994</v>
-      </c>
-      <c r="F31">
-        <v>24.3</v>
-      </c>
-      <c r="G31">
-        <v>5.3</v>
-      </c>
-      <c r="H31">
-        <v>53.5</v>
-      </c>
-      <c r="J31" s="24"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
-      <c r="P31" s="24"/>
-    </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="J32" s="24"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
-      <c r="P32" s="24"/>
-    </row>
-    <row r="33" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J33" s="24"/>
-      <c r="K33" s="24"/>
-      <c r="L33" s="24"/>
-      <c r="P33" s="24"/>
-    </row>
-    <row r="34" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J34" s="24"/>
-      <c r="K34" s="24"/>
-      <c r="L34" s="24"/>
-      <c r="P34" s="24"/>
-    </row>
-    <row r="35" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J35" s="24"/>
-      <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
-      <c r="P35" s="24"/>
-    </row>
-    <row r="36" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J36" s="24"/>
-      <c r="K36" s="24"/>
-      <c r="L36" s="24"/>
-      <c r="P36" s="24"/>
-    </row>
-    <row r="37" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J37" s="24"/>
-      <c r="K37" s="24"/>
-      <c r="L37" s="24"/>
-      <c r="P37" s="24"/>
-    </row>
-    <row r="38" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J38" s="24"/>
-      <c r="K38" s="24"/>
-      <c r="L38" s="24"/>
-      <c r="P38" s="24"/>
-    </row>
-    <row r="39" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J39" s="24"/>
-      <c r="K39" s="24"/>
-      <c r="L39" s="24"/>
-      <c r="P39" s="24"/>
-    </row>
-    <row r="40" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J40" s="24"/>
-      <c r="K40" s="24"/>
-      <c r="L40" s="24"/>
-      <c r="P40" s="24"/>
-    </row>
-    <row r="41" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J41" s="24"/>
-      <c r="K41" s="24"/>
-      <c r="L41" s="24"/>
-      <c r="P41" s="24"/>
-    </row>
-    <row r="42" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J42" s="24"/>
-      <c r="K42" s="24"/>
-      <c r="L42" s="24"/>
-      <c r="P42" s="24"/>
-    </row>
-    <row r="43" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J43" s="24"/>
-      <c r="K43" s="24"/>
-      <c r="L43" s="24"/>
-      <c r="P43" s="24"/>
-    </row>
-    <row r="44" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J44" s="24"/>
-      <c r="K44" s="24"/>
-      <c r="L44" s="24"/>
-      <c r="P44" s="24"/>
-    </row>
-    <row r="45" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J45" s="24"/>
-      <c r="K45" s="24"/>
-      <c r="L45" s="24"/>
-      <c r="P45" s="24"/>
-    </row>
-    <row r="46" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J46" s="24"/>
-      <c r="K46" s="24"/>
-      <c r="L46" s="24"/>
-      <c r="P46" s="24"/>
-    </row>
-    <row r="47" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J47" s="24"/>
-      <c r="K47" s="24"/>
-      <c r="L47" s="24"/>
-      <c r="P47" s="24"/>
-    </row>
-    <row r="48" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J48" s="24"/>
-      <c r="K48" s="24"/>
-      <c r="L48" s="24"/>
-      <c r="P48" s="24"/>
-    </row>
-    <row r="49" spans="6:16" x14ac:dyDescent="0.35">
-      <c r="J49" s="24"/>
-      <c r="K49" s="24"/>
-      <c r="L49" s="24"/>
-      <c r="P49" s="24"/>
-    </row>
-    <row r="50" spans="6:16" x14ac:dyDescent="0.35">
-      <c r="G50" t="s">
-        <v>39</v>
-      </c>
-      <c r="H50" t="s">
-        <v>41</v>
-      </c>
-      <c r="I50" t="s">
-        <v>40</v>
-      </c>
-      <c r="J50" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="K50" s="24"/>
-      <c r="L50" s="24"/>
-      <c r="P50" s="24"/>
-    </row>
-    <row r="51" spans="6:16" x14ac:dyDescent="0.35">
-      <c r="F51" t="s">
-        <v>42</v>
-      </c>
-      <c r="G51">
-        <v>2</v>
-      </c>
-      <c r="H51">
-        <v>1</v>
-      </c>
-      <c r="I51" s="25">
-        <v>3</v>
-      </c>
-      <c r="J51" s="12">
-        <v>6</v>
-      </c>
-      <c r="K51" s="24"/>
-      <c r="L51" s="24"/>
-      <c r="P51" s="24"/>
-    </row>
-    <row r="52" spans="6:16" x14ac:dyDescent="0.35">
-      <c r="F52" t="s">
-        <v>43</v>
-      </c>
-      <c r="G52">
-        <v>2</v>
-      </c>
-      <c r="H52" s="25">
-        <v>2</v>
-      </c>
-      <c r="I52" s="25">
-        <v>2</v>
-      </c>
-      <c r="J52" s="12">
-        <v>6</v>
-      </c>
-      <c r="K52" s="24"/>
-      <c r="L52" s="24"/>
-    </row>
-    <row r="53" spans="6:16" x14ac:dyDescent="0.35">
-      <c r="F53" t="s">
-        <v>44</v>
-      </c>
-      <c r="G53" s="25">
-        <v>4</v>
-      </c>
-      <c r="H53">
-        <v>1</v>
-      </c>
-      <c r="I53" s="25">
-        <v>3</v>
-      </c>
-      <c r="J53" s="12">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="6:16" x14ac:dyDescent="0.35">
-      <c r="F54" t="s">
-        <v>45</v>
-      </c>
-      <c r="G54">
-        <v>2</v>
-      </c>
-      <c r="H54">
-        <v>1</v>
-      </c>
-      <c r="I54">
-        <v>1</v>
-      </c>
-      <c r="J54" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="6:16" x14ac:dyDescent="0.35">
-      <c r="F55" t="s">
-        <v>46</v>
-      </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-      <c r="I55">
-        <v>5</v>
-      </c>
-      <c r="J55" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" spans="6:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F56" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G56" s="11">
-        <v>10</v>
-      </c>
-      <c r="H56" s="11">
-        <v>5</v>
-      </c>
-      <c r="I56" s="11">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="57" spans="6:16" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
-    <row r="67" spans="5:13" x14ac:dyDescent="0.35">
-      <c r="E67" t="s">
-        <v>49</v>
-      </c>
-      <c r="F67" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="G67" s="23"/>
-      <c r="H67" s="23"/>
-      <c r="I67" s="23"/>
-      <c r="J67" s="23"/>
-      <c r="K67" s="23"/>
-    </row>
-    <row r="68" spans="5:13" x14ac:dyDescent="0.35">
-      <c r="E68" t="s">
-        <v>50</v>
-      </c>
-      <c r="F68" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="69" spans="5:13" x14ac:dyDescent="0.35">
-      <c r="F69" t="s">
-        <v>52</v>
-      </c>
-      <c r="M69">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="5:13" x14ac:dyDescent="0.35">
-      <c r="F70" s="18" t="s">
+    </row>
+    <row r="123" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="F123" s="18" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="71" spans="5:13" x14ac:dyDescent="0.35">
-      <c r="F71" t="s">
+    <row r="124" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="F124" t="s">
         <v>59</v>
       </c>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
-      <c r="K71" s="1"/>
-    </row>
-    <row r="72" spans="5:13" x14ac:dyDescent="0.35">
-      <c r="E72" t="s">
+      <c r="H124" s="1"/>
+      <c r="I124" s="1"/>
+      <c r="J124" s="1"/>
+      <c r="K124" s="1"/>
+    </row>
+    <row r="125" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E125" t="s">
         <v>54</v>
       </c>
-      <c r="F72" t="s">
+      <c r="F125" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="73" spans="5:13" x14ac:dyDescent="0.35">
-      <c r="E73" s="13" t="s">
+    <row r="126" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E126" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="F73" s="13" t="s">
+      <c r="F126" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
+      <c r="G126" s="13"/>
+      <c r="H126" s="13"/>
+      <c r="I126" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="F67:K67"/>
+    <mergeCell ref="F120:K120"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F18" location="'Stage 1'!A1" display="VP6" xr:uid="{11E86EC5-B611-4BFA-BA48-BEFD10AC62C8}"/>
-    <hyperlink ref="F19" location="'Stage 1'!A1" display="VP7" xr:uid="{CC8CB78E-623A-44BF-98AC-AF14F818CE53}"/>
+    <hyperlink ref="F22:H22" location="'Stage 2'!A1" display="VP7" xr:uid="{2B4ED8AD-B24C-4E8E-9420-3731BA3BA9D5}"/>
+    <hyperlink ref="N20:P23" location="'Stage 2'!A1" display="VP9" xr:uid="{7C87BFEB-33B4-493E-9594-498C850507D7}"/>
+    <hyperlink ref="R20:T24" location="'Stage 2'!A1" display="HLA411" xr:uid="{6CF2B8B5-90E7-43A3-9280-8DD9E0270956}"/>
+    <hyperlink ref="B47:E47" location="'Stage 2'!A1" display="VP7" xr:uid="{52BF13D5-7207-44AA-83C1-8D09EA8639B1}"/>
+    <hyperlink ref="B60:E60" location="'Stage 2'!A1" display="VP7" xr:uid="{60195519-1514-4352-9F21-58600A74A60C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83567D3B-F48D-486C-96F8-0F8805A7B8A0}">
-  <dimension ref="B2:H5"/>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E062963-C822-49F3-9665-072206D37919}">
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="11.453125" customWidth="1"/>
-    <col min="3" max="3" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="9.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B2" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="14">
-        <v>68.8</v>
-      </c>
-      <c r="E3" s="14">
-        <v>83.4</v>
-      </c>
-      <c r="F3">
-        <v>19.8</v>
-      </c>
-      <c r="G3" s="13">
-        <v>38.200000000000003</v>
-      </c>
-      <c r="H3" s="14">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="13">
-        <v>69.2</v>
-      </c>
-      <c r="E4" s="14">
-        <v>83</v>
-      </c>
-      <c r="F4" s="14">
-        <v>91</v>
-      </c>
-      <c r="G4">
-        <v>56.2</v>
-      </c>
-      <c r="H4" s="14">
-        <v>79.8</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="14">
-        <v>19.8</v>
-      </c>
-      <c r="E5" s="14">
-        <v>33.200000000000003</v>
-      </c>
-      <c r="F5" s="14">
-        <v>95.3</v>
-      </c>
-      <c r="G5" s="14">
-        <v>57.9</v>
-      </c>
-      <c r="H5" s="13">
-        <v>12.4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24775ADE-03D3-4D0A-807B-37E1A793A03E}">
-  <dimension ref="B3:AE12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="12" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="15.26953125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:31" x14ac:dyDescent="0.35">
-      <c r="B3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P3" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>23</v>
-      </c>
-      <c r="R3" t="s">
-        <v>24</v>
-      </c>
-      <c r="S3" t="s">
-        <v>26</v>
-      </c>
-      <c r="T3" t="s">
-        <v>27</v>
-      </c>
-      <c r="U3" t="s">
-        <v>28</v>
-      </c>
-      <c r="V3" t="s">
-        <v>29</v>
-      </c>
-      <c r="W3" t="s">
-        <v>30</v>
-      </c>
-      <c r="X3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="2:31" x14ac:dyDescent="0.35">
-      <c r="B4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" t="s">
-        <v>8</v>
-      </c>
-      <c r="M4" t="s">
-        <v>19</v>
-      </c>
-      <c r="N4" t="s">
-        <v>19</v>
-      </c>
-      <c r="O4" t="s">
-        <v>19</v>
-      </c>
-      <c r="P4" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>19</v>
-      </c>
-      <c r="R4" t="s">
-        <v>25</v>
-      </c>
-      <c r="S4" t="s">
-        <v>25</v>
-      </c>
-      <c r="T4" t="s">
-        <v>25</v>
-      </c>
-      <c r="U4" t="s">
-        <v>25</v>
-      </c>
-      <c r="V4" t="s">
-        <v>25</v>
-      </c>
-      <c r="W4" t="s">
-        <v>25</v>
-      </c>
-      <c r="X4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="2:31" x14ac:dyDescent="0.35">
-      <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="8">
-        <v>84</v>
-      </c>
-      <c r="D5">
-        <v>79.8</v>
-      </c>
-      <c r="E5">
-        <v>57.9</v>
-      </c>
-      <c r="F5">
-        <v>31.2</v>
-      </c>
-      <c r="G5" s="8">
-        <v>65</v>
-      </c>
-      <c r="H5">
-        <v>43.2</v>
-      </c>
-      <c r="I5">
-        <v>8.6</v>
-      </c>
-      <c r="J5">
-        <v>30.2</v>
-      </c>
-      <c r="K5">
-        <v>22.2</v>
-      </c>
-      <c r="L5">
-        <v>35.700000000000003</v>
-      </c>
-      <c r="M5" s="8">
-        <v>90.3</v>
-      </c>
-      <c r="N5">
-        <v>19.7</v>
-      </c>
-      <c r="O5" s="8">
-        <v>84.7</v>
-      </c>
-      <c r="P5" s="8">
-        <v>66.7</v>
-      </c>
-      <c r="Q5">
-        <v>36.1</v>
-      </c>
-      <c r="R5">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="S5">
-        <v>89.7</v>
-      </c>
-      <c r="T5">
-        <v>54.7</v>
-      </c>
-      <c r="U5">
-        <v>28.7</v>
-      </c>
-      <c r="V5">
-        <v>46.3</v>
-      </c>
-      <c r="W5">
-        <v>41.7</v>
-      </c>
-      <c r="X5" s="7">
-        <v>91.7</v>
-      </c>
-      <c r="Y5" s="7">
-        <v>63.8</v>
-      </c>
-      <c r="Z5">
-        <v>4.8</v>
-      </c>
-      <c r="AA5">
-        <v>29.2</v>
-      </c>
-      <c r="AB5">
-        <v>7.1</v>
-      </c>
-      <c r="AC5" s="7">
-        <v>53.5</v>
-      </c>
-      <c r="AD5" s="7">
-        <v>31.9</v>
-      </c>
-      <c r="AE5" s="7">
-        <v>95.9</v>
-      </c>
-    </row>
-    <row r="6" spans="2:31" x14ac:dyDescent="0.35">
-      <c r="B6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="4">
-        <v>83.4</v>
-      </c>
-      <c r="D6">
-        <v>83</v>
-      </c>
-      <c r="E6">
-        <v>33.200000000000003</v>
-      </c>
-      <c r="F6">
-        <v>84.4</v>
-      </c>
-      <c r="G6">
-        <v>1.3</v>
-      </c>
-      <c r="H6" s="4">
-        <v>84.7</v>
-      </c>
-      <c r="I6">
-        <v>16.8</v>
-      </c>
-      <c r="J6">
-        <v>24.1</v>
-      </c>
-      <c r="K6">
-        <v>64.900000000000006</v>
-      </c>
-      <c r="L6">
-        <v>84</v>
-      </c>
-      <c r="M6" s="4">
-        <v>46</v>
-      </c>
-      <c r="N6">
-        <v>52.8</v>
-      </c>
-      <c r="O6">
-        <v>40.4</v>
-      </c>
-      <c r="P6" s="4">
-        <v>60.3</v>
-      </c>
-      <c r="Q6">
-        <v>45</v>
-      </c>
-      <c r="R6">
-        <v>72.5</v>
-      </c>
-      <c r="S6" s="4">
-        <v>99</v>
-      </c>
-      <c r="T6">
-        <v>20.9</v>
-      </c>
-      <c r="U6">
-        <v>22.8</v>
-      </c>
-      <c r="V6">
-        <v>4.8</v>
-      </c>
-      <c r="W6">
-        <v>5.9</v>
-      </c>
-      <c r="X6" s="8">
-        <v>71.5</v>
-      </c>
-      <c r="Y6">
-        <v>63.3</v>
-      </c>
-      <c r="Z6">
-        <v>50.4</v>
-      </c>
-      <c r="AA6" s="4">
-        <v>95.8</v>
-      </c>
-      <c r="AB6" s="8">
-        <v>93.3</v>
-      </c>
-      <c r="AC6" s="8">
-        <v>77.599999999999994</v>
-      </c>
-      <c r="AD6">
-        <v>13.3</v>
-      </c>
-      <c r="AE6">
-        <v>9.9</v>
-      </c>
-    </row>
-    <row r="7" spans="2:31" x14ac:dyDescent="0.35">
-      <c r="B7" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>68.8</v>
-      </c>
-      <c r="D7">
-        <v>69.2</v>
-      </c>
-      <c r="E7">
-        <v>19.8</v>
-      </c>
-      <c r="F7" s="3">
-        <v>98.5</v>
-      </c>
-      <c r="G7">
-        <v>39.6</v>
-      </c>
-      <c r="H7">
-        <v>67.900000000000006</v>
-      </c>
-      <c r="I7">
-        <v>44.5</v>
-      </c>
-      <c r="J7">
-        <v>46.3</v>
-      </c>
-      <c r="K7" s="3">
-        <v>96.8</v>
-      </c>
-      <c r="L7">
-        <v>78.900000000000006</v>
-      </c>
-      <c r="M7" s="8">
-        <v>50.9</v>
-      </c>
-      <c r="N7" s="3">
-        <v>76.7</v>
-      </c>
-      <c r="O7">
-        <v>28.3</v>
-      </c>
-      <c r="P7">
-        <v>8.5</v>
-      </c>
-      <c r="Q7">
-        <v>14.3</v>
-      </c>
-      <c r="R7">
-        <v>47.4</v>
-      </c>
-      <c r="S7">
-        <v>58.9</v>
-      </c>
-      <c r="T7">
-        <v>55.1</v>
-      </c>
-      <c r="U7">
-        <v>16.3</v>
-      </c>
-      <c r="V7" s="3">
-        <v>83.9</v>
-      </c>
-      <c r="W7" s="3">
-        <v>70</v>
-      </c>
-      <c r="X7">
-        <v>52.5</v>
-      </c>
-      <c r="Y7">
-        <v>3.4</v>
-      </c>
-      <c r="Z7" s="3">
-        <v>57.9</v>
-      </c>
-      <c r="AA7">
-        <v>93.4</v>
-      </c>
-      <c r="AB7">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="AC7">
-        <v>15.6</v>
-      </c>
-      <c r="AD7">
-        <v>17.2</v>
-      </c>
-      <c r="AE7">
-        <v>5.0999999999999996</v>
-      </c>
-    </row>
-    <row r="8" spans="2:31" x14ac:dyDescent="0.35">
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>38.200000000000003</v>
-      </c>
-      <c r="D8">
-        <v>56.2</v>
-      </c>
-      <c r="E8">
-        <v>12.4</v>
-      </c>
-      <c r="F8">
-        <v>83</v>
-      </c>
-      <c r="G8">
-        <v>26.3</v>
-      </c>
-      <c r="H8">
-        <v>21.3</v>
-      </c>
-      <c r="I8" s="6">
-        <v>76.400000000000006</v>
-      </c>
-      <c r="J8">
-        <v>47.8</v>
-      </c>
-      <c r="K8">
-        <v>78.8</v>
-      </c>
-      <c r="L8" s="6">
-        <v>89.1</v>
-      </c>
-      <c r="M8">
-        <v>7.4</v>
-      </c>
-      <c r="N8">
-        <v>0.7</v>
-      </c>
-      <c r="O8" s="6">
-        <v>43.9</v>
-      </c>
-      <c r="P8">
-        <v>31.8</v>
-      </c>
-      <c r="Q8">
-        <v>51.8</v>
-      </c>
-      <c r="R8" s="8">
-        <v>84.3</v>
-      </c>
-      <c r="S8">
-        <v>57.6</v>
-      </c>
-      <c r="T8">
-        <v>77.8</v>
-      </c>
-      <c r="U8" s="6">
-        <v>96.9</v>
-      </c>
-      <c r="V8">
-        <v>58.1</v>
-      </c>
-      <c r="W8">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="X8">
-        <v>70.3</v>
-      </c>
-      <c r="Y8" s="8">
-        <v>70.5</v>
-      </c>
-      <c r="Z8" s="8">
-        <v>63.4</v>
-      </c>
-      <c r="AA8">
-        <v>81.599999999999994</v>
-      </c>
-      <c r="AB8">
-        <v>63.2</v>
-      </c>
-      <c r="AC8">
-        <v>5.3</v>
-      </c>
-      <c r="AD8">
-        <v>31.2</v>
-      </c>
-      <c r="AE8" s="8">
-        <v>85.5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:31" x14ac:dyDescent="0.35">
-      <c r="B9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9">
-        <v>19.8</v>
-      </c>
-      <c r="D9" s="5">
-        <v>91</v>
-      </c>
-      <c r="E9" s="5">
-        <v>95.3</v>
-      </c>
-      <c r="F9">
-        <v>7.2</v>
-      </c>
-      <c r="G9" s="5">
-        <v>54.9</v>
-      </c>
-      <c r="H9">
-        <v>35.700000000000003</v>
-      </c>
-      <c r="I9">
-        <v>73.099999999999994</v>
-      </c>
-      <c r="J9" s="5">
-        <v>87.1</v>
-      </c>
-      <c r="K9">
-        <v>7</v>
-      </c>
-      <c r="L9">
-        <v>22.4</v>
-      </c>
-      <c r="M9">
-        <v>7.2</v>
-      </c>
-      <c r="N9">
-        <v>1.3</v>
-      </c>
-      <c r="O9">
-        <v>12.6</v>
-      </c>
-      <c r="P9">
-        <v>27.9</v>
-      </c>
-      <c r="Q9" s="5">
-        <v>73.3</v>
-      </c>
-      <c r="R9" s="5">
-        <v>74.900000000000006</v>
-      </c>
-      <c r="S9">
-        <v>92.4</v>
-      </c>
-      <c r="T9" s="5">
-        <v>86</v>
-      </c>
-      <c r="U9">
-        <v>82</v>
-      </c>
-      <c r="V9">
-        <v>70.2</v>
-      </c>
-      <c r="W9">
-        <v>26.7</v>
-      </c>
-      <c r="X9">
-        <v>7</v>
-      </c>
-      <c r="Y9">
-        <v>36.200000000000003</v>
-      </c>
-      <c r="Z9">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="AA9">
-        <v>58.4</v>
-      </c>
-      <c r="AB9" s="5">
-        <v>64.900000000000006</v>
-      </c>
-      <c r="AC9">
-        <v>24.3</v>
-      </c>
-      <c r="AD9" s="8">
-        <v>48.1</v>
-      </c>
-      <c r="AE9">
-        <v>60.4</v>
-      </c>
-    </row>
-    <row r="10" spans="2:31" x14ac:dyDescent="0.35">
-      <c r="B10" s="1"/>
-      <c r="C10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-    </row>
-    <row r="11" spans="2:31" x14ac:dyDescent="0.35">
-      <c r="B11" s="1"/>
-      <c r="C11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-    </row>
-    <row r="12" spans="2:31" x14ac:dyDescent="0.35">
-      <c r="B12" s="1"/>
-      <c r="C12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="B3:AE12" xr:uid="{24775ADE-03D3-4D0A-807B-37E1A793A03E}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:AE12">
-      <sortCondition descending="1" ref="C3:C12"/>
-    </sortState>
-  </autoFilter>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/1.training_model/supplementary/Data Tabulation - Flowchart.xlsx
+++ b/1.training_model/supplementary/Data Tabulation - Flowchart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sitisyaziyah\source\repos\DeviceCluster\1.training_model\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C0C5EC6-8649-4EC9-AEF6-278AD5FCC829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{971519B7-5377-4244-AFDD-99390543FF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="717" firstSheet="2" activeTab="3" xr2:uid="{E471D6E3-533D-4285-ABDC-6FF3DFDEE99D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="717" firstSheet="2" activeTab="9" xr2:uid="{E471D6E3-533D-4285-ABDC-6FF3DFDEE99D}"/>
   </bookViews>
   <sheets>
     <sheet name="Obs-flowchart" sheetId="19" state="hidden" r:id="rId1"/>
@@ -528,7 +528,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -587,7 +587,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -14447,11 +14446,6 @@
       </c>
       <c r="T31" s="23"/>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="R32" s="40"/>
-      <c r="S32" s="40"/>
-      <c r="T32" s="40"/>
-    </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A33" s="33"/>
       <c r="B33" s="33"/>
@@ -14842,11 +14836,6 @@
         <v>25</v>
       </c>
       <c r="T47" s="23"/>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="R48" s="40"/>
-      <c r="S48" s="40"/>
-      <c r="T48" s="40"/>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A49" s="33"/>

--- a/1.training_model/supplementary/Data Tabulation - Flowchart.xlsx
+++ b/1.training_model/supplementary/Data Tabulation - Flowchart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sitisyaziyah\source\repos\DeviceCluster\1.training_model\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{971519B7-5377-4244-AFDD-99390543FF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C177ABD-7CF8-4571-93F1-94E5AF7E7F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="717" firstSheet="2" activeTab="9" xr2:uid="{E471D6E3-533D-4285-ABDC-6FF3DFDEE99D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="717" firstSheet="3" activeTab="10" xr2:uid="{E471D6E3-533D-4285-ABDC-6FF3DFDEE99D}"/>
   </bookViews>
   <sheets>
     <sheet name="Obs-flowchart" sheetId="19" state="hidden" r:id="rId1"/>
@@ -23,7 +23,8 @@
     <sheet name="Stage 2" sheetId="6" r:id="rId8"/>
     <sheet name="Stage 3" sheetId="7" r:id="rId9"/>
     <sheet name="Stage 4" sheetId="13" r:id="rId10"/>
-    <sheet name="transpose" sheetId="3" state="hidden" r:id="rId11"/>
+    <sheet name="try and error" sheetId="24" r:id="rId11"/>
+    <sheet name="transpose" sheetId="3" state="hidden" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Draft Data'!#REF!</definedName>
@@ -31,7 +32,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Stage 2'!$B$2:$H$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Stage 3'!$B$2:$H$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Stage 4'!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">transpose!$B$3:$AE$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">transpose!$B$3:$AE$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -11965,6 +11966,72 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>501650</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>157875</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFB743D4-5788-2011-A2EC-588B2A2894CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3124200" y="361950"/>
+          <a:ext cx="5911850" cy="3294775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -12825,6 +12892,16 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4779006-2C51-4123-8965-52E24C209B6E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24775ADE-03D3-4D0A-807B-37E1A793A03E}">
   <dimension ref="B3:AE12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
